--- a/DataAnalysis/LF/0.05/Results.xlsx
+++ b/DataAnalysis/LF/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LF\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18CCE69-FA1D-41A0-8526-3DDC21500AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214D5FAB-5D47-48EC-8093-4325606B8C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -998,34 +998,34 @@
         <v>64</v>
       </c>
       <c r="G19">
-        <v>19.5625</v>
+        <v>18.75</v>
       </c>
       <c r="H19">
-        <v>3.2997564845216774</v>
+        <v>1.7559422921421233</v>
       </c>
       <c r="I19">
-        <v>8.8125</v>
+        <v>10.5</v>
       </c>
       <c r="J19">
-        <v>2.0863074009907003</v>
+        <v>2.2730302828309759</v>
       </c>
       <c r="K19">
-        <v>27.4375</v>
+        <v>27.125</v>
       </c>
       <c r="L19">
-        <v>1.2374368670764582</v>
+        <v>1.9311050377094112</v>
       </c>
       <c r="M19">
-        <v>18.604166666666668</v>
+        <v>18.791666666666664</v>
       </c>
       <c r="N19">
-        <v>1.4473223771821069</v>
+        <v>1.1252571722516165</v>
       </c>
       <c r="O19">
-        <v>9.7916666666666661</v>
+        <v>8.2916666666666661</v>
       </c>
       <c r="P19">
-        <v>1.6250763107845259</v>
+        <v>1.1970256348008435</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
@@ -4637,23 +4637,23 @@
         <v>74</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R34" si="0">AVERAGE(C3:D3)</f>
+        <f t="shared" ref="R3:R11" si="0">AVERAGE(C3:D3)</f>
         <v>22.5</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S34" si="1">AVERAGE(H3,I3)</f>
+        <f t="shared" ref="S3:S11" si="1">AVERAGE(H3,I3)</f>
         <v>17</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T34" si="2">AVERAGE(M3:N3)</f>
+        <f t="shared" ref="T3:T11" si="2">AVERAGE(M3:N3)</f>
         <v>28</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U34" si="3">AVERAGE(R3:T3)</f>
+        <f t="shared" ref="U3:U11" si="3">AVERAGE(R3:T3)</f>
         <v>22.5</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD34" si="4">MIN(R3:T3)</f>
+        <f t="shared" ref="AD3:AD11" si="4">MIN(R3:T3)</f>
         <v>17</v>
       </c>
       <c r="AE3">
@@ -10364,7 +10364,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -10571,23 +10571,23 @@
         <v>69</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q11" si="0">AVERAGE(C5,D5)</f>
+        <f t="shared" ref="Q5" si="0">AVERAGE(C5,D5)</f>
         <v>18</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R11" si="1">AVERAGE(H5,I5)</f>
+        <f t="shared" ref="R5" si="1">AVERAGE(H5,I5)</f>
         <v>9</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S11" si="2">AVERAGE(M5,N5)</f>
+        <f t="shared" ref="S5" si="2">AVERAGE(M5,N5)</f>
         <v>26</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T11" si="3">AVERAGE(Q5:S5)</f>
+        <f t="shared" ref="T5" si="3">AVERAGE(Q5:S5)</f>
         <v>17.666666666666668</v>
       </c>
       <c r="AC5">
-        <f t="shared" ref="AC5:AC11" si="4">MIN(Q5:S5)</f>
+        <f t="shared" ref="AC5" si="4">MIN(Q5:S5)</f>
         <v>9</v>
       </c>
       <c r="AD5">
@@ -10720,6 +10720,170 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>6.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>64</v>
+      </c>
+      <c r="C9">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>87</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>89</v>
+      </c>
+      <c r="L9">
+        <v>93</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <v>46</v>
+      </c>
+      <c r="O9">
+        <v>54</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q8:Q10" si="11">AVERAGE(C9,D9)</f>
+        <v>24.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R8:R10" si="12">AVERAGE(H9,I9)</f>
+        <v>9.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S8:S10" si="13">AVERAGE(M9,N9)</f>
+        <v>26.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T8:T10" si="14">AVERAGE(Q9:S9)</f>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U9">
+        <f>AVERAGE(Q9:Q12)</f>
+        <v>22.25</v>
+      </c>
+      <c r="V9">
+        <f>_xlfn.STDEV.S(Q9:Q12)</f>
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="W9">
+        <f>AVERAGE(R9:R12)</f>
+        <v>10.75</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.STDEV.S(R9:R12)</f>
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="Y9">
+        <f>AVERAGE(S9:S12)</f>
+        <v>27</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.STDEV.S(S9:S12)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="AA9">
+        <f>AVERAGE(T9:T12)</f>
+        <v>20</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.STDEV.S(T9:T12)</f>
+        <v>0.2357022603955175</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC8:AC10" si="15">MIN(Q9:S9)</f>
+        <v>9.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD8:AD10" si="16">(T9-AC9)</f>
+        <v>10.666666666666668</v>
+      </c>
+      <c r="AE9">
+        <f>AVERAGE(AD9:AD12)</f>
+        <v>9.25</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.STDEV.S(AD9:AD12)</f>
+        <v>2.0034692133618837</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>22</v>
+      </c>
+      <c r="E10">
+        <v>78</v>
+      </c>
+      <c r="G10">
+        <v>89</v>
+      </c>
+      <c r="H10">
+        <v>11</v>
+      </c>
+      <c r="I10">
+        <v>13</v>
+      </c>
+      <c r="J10">
+        <v>87</v>
+      </c>
+      <c r="L10">
+        <v>75</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <v>30</v>
+      </c>
+      <c r="O10">
+        <v>70</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="13"/>
+        <v>27.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="14"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="16"/>
+        <v>7.8333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -11200,7 +11364,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF11"/>
+  <dimension ref="A2:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11407,23 +11571,23 @@
         <v>65</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q12" si="0">AVERAGE(C5,D5)</f>
+        <f t="shared" ref="Q5" si="0">AVERAGE(C5,D5)</f>
         <v>16.5</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R12" si="1">AVERAGE(H5,I5)</f>
+        <f t="shared" ref="R5" si="1">AVERAGE(H5,I5)</f>
         <v>11.5</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S12" si="2">AVERAGE(M5,N5)</f>
+        <f t="shared" ref="S5" si="2">AVERAGE(M5,N5)</f>
         <v>28</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T12" si="3">AVERAGE(Q5:S5)</f>
+        <f t="shared" ref="T5" si="3">AVERAGE(Q5:S5)</f>
         <v>18.666666666666668</v>
       </c>
       <c r="AC5">
-        <f t="shared" ref="AC5:AC12" si="4">MIN(Q5:S5)</f>
+        <f t="shared" ref="AC5" si="4">MIN(Q5:S5)</f>
         <v>11.5</v>
       </c>
       <c r="AD5">
@@ -11804,6 +11968,294 @@
       <c r="AD11">
         <f t="shared" si="5"/>
         <v>9.8333333333333321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>79</v>
+      </c>
+      <c r="C13">
+        <v>21</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>94</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>82</v>
+      </c>
+      <c r="L13">
+        <v>81</v>
+      </c>
+      <c r="M13">
+        <v>19</v>
+      </c>
+      <c r="N13">
+        <v>35</v>
+      </c>
+      <c r="O13">
+        <v>65</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" ref="Q12:Q16" si="11">AVERAGE(C13,D13)</f>
+        <v>20.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" ref="R12:R16" si="12">AVERAGE(H13,I13)</f>
+        <v>12</v>
+      </c>
+      <c r="S13">
+        <f t="shared" ref="S12:S16" si="13">AVERAGE(M13,N13)</f>
+        <v>27</v>
+      </c>
+      <c r="T13">
+        <f t="shared" ref="T12:T16" si="14">AVERAGE(Q13:S13)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U13">
+        <f>AVERAGE(Q13:Q20)</f>
+        <v>18.75</v>
+      </c>
+      <c r="V13">
+        <f>_xlfn.STDEV.S(Q13:Q20)</f>
+        <v>1.7559422921421233</v>
+      </c>
+      <c r="W13">
+        <f>AVERAGE(R13:R20)</f>
+        <v>10.5</v>
+      </c>
+      <c r="X13">
+        <f>_xlfn.STDEV.S(R13:R20)</f>
+        <v>2.2730302828309759</v>
+      </c>
+      <c r="Y13">
+        <f>AVERAGE(S13:S20)</f>
+        <v>27.125</v>
+      </c>
+      <c r="Z13">
+        <f>_xlfn.STDEV.S(S13:S20)</f>
+        <v>1.9311050377094112</v>
+      </c>
+      <c r="AA13">
+        <f>AVERAGE(T13:T20)</f>
+        <v>18.791666666666664</v>
+      </c>
+      <c r="AB13">
+        <f>_xlfn.STDEV.S(T13:T20)</f>
+        <v>1.1252571722516165</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" ref="AC12:AC16" si="15">MIN(Q13:S13)</f>
+        <v>12</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" ref="AD12:AD16" si="16">(T13-AC13)</f>
+        <v>7.8333333333333321</v>
+      </c>
+      <c r="AE13">
+        <f>AVERAGE(AD13:AD20)</f>
+        <v>8.2916666666666661</v>
+      </c>
+      <c r="AF13">
+        <f>_xlfn.STDEV.S(AD13:AD20)</f>
+        <v>1.1970256348008435</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>78</v>
+      </c>
+      <c r="C14">
+        <v>22</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>87</v>
+      </c>
+      <c r="G14">
+        <v>96</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>16</v>
+      </c>
+      <c r="J14">
+        <v>84</v>
+      </c>
+      <c r="L14">
+        <v>93</v>
+      </c>
+      <c r="M14">
+        <v>7</v>
+      </c>
+      <c r="N14">
+        <v>49</v>
+      </c>
+      <c r="O14">
+        <v>51</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="11"/>
+        <v>17.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="13"/>
+        <v>28</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="14"/>
+        <v>18.5</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="16"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>69</v>
+      </c>
+      <c r="C15">
+        <v>31</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>91</v>
+      </c>
+      <c r="G15">
+        <v>94</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>9</v>
+      </c>
+      <c r="J15">
+        <v>91</v>
+      </c>
+      <c r="L15">
+        <v>80</v>
+      </c>
+      <c r="M15">
+        <v>20</v>
+      </c>
+      <c r="N15">
+        <v>29</v>
+      </c>
+      <c r="O15">
+        <v>71</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="12"/>
+        <v>7.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="13"/>
+        <v>24.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="14"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="15"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="16"/>
+        <v>9.8333333333333321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>17</v>
+      </c>
+      <c r="E16">
+        <v>83</v>
+      </c>
+      <c r="G16">
+        <v>89</v>
+      </c>
+      <c r="H16">
+        <v>11</v>
+      </c>
+      <c r="I16">
+        <v>14</v>
+      </c>
+      <c r="J16">
+        <v>86</v>
+      </c>
+      <c r="L16">
+        <v>93</v>
+      </c>
+      <c r="M16">
+        <v>7</v>
+      </c>
+      <c r="N16">
+        <v>51</v>
+      </c>
+      <c r="O16">
+        <v>49</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="12"/>
+        <v>12.5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="14"/>
+        <v>19.5</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="15"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="16"/>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/LF/0.05/Results.xlsx
+++ b/DataAnalysis/LF/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LF\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214D5FAB-5D47-48EC-8093-4325606B8C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E56454D-D44E-4F2F-8F68-70983CB2E213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10760,19 +10760,19 @@
         <v>54</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q8:Q10" si="11">AVERAGE(C9,D9)</f>
+        <f t="shared" ref="Q9:Q10" si="11">AVERAGE(C9,D9)</f>
         <v>24.5</v>
       </c>
       <c r="R9">
-        <f t="shared" ref="R8:R10" si="12">AVERAGE(H9,I9)</f>
+        <f t="shared" ref="R9:R10" si="12">AVERAGE(H9,I9)</f>
         <v>9.5</v>
       </c>
       <c r="S9">
-        <f t="shared" ref="S8:S10" si="13">AVERAGE(M9,N9)</f>
+        <f t="shared" ref="S9:S10" si="13">AVERAGE(M9,N9)</f>
         <v>26.5</v>
       </c>
       <c r="T9">
-        <f t="shared" ref="T8:T10" si="14">AVERAGE(Q9:S9)</f>
+        <f t="shared" ref="T9:T10" si="14">AVERAGE(Q9:S9)</f>
         <v>20.166666666666668</v>
       </c>
       <c r="U9">
@@ -10808,11 +10808,11 @@
         <v>0.2357022603955175</v>
       </c>
       <c r="AC9">
-        <f t="shared" ref="AC8:AC10" si="15">MIN(Q9:S9)</f>
+        <f t="shared" ref="AC9:AC10" si="15">MIN(Q9:S9)</f>
         <v>9.5</v>
       </c>
       <c r="AD9">
-        <f t="shared" ref="AD8:AD10" si="16">(T9-AC9)</f>
+        <f t="shared" ref="AD9:AD10" si="16">(T9-AC9)</f>
         <v>10.666666666666668</v>
       </c>
       <c r="AE9">
@@ -12008,19 +12008,19 @@
         <v>65</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q12:Q16" si="11">AVERAGE(C13,D13)</f>
+        <f t="shared" ref="Q13:Q16" si="11">AVERAGE(C13,D13)</f>
         <v>20.5</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R12:R16" si="12">AVERAGE(H13,I13)</f>
+        <f t="shared" ref="R13:R16" si="12">AVERAGE(H13,I13)</f>
         <v>12</v>
       </c>
       <c r="S13">
-        <f t="shared" ref="S12:S16" si="13">AVERAGE(M13,N13)</f>
+        <f t="shared" ref="S13:S16" si="13">AVERAGE(M13,N13)</f>
         <v>27</v>
       </c>
       <c r="T13">
-        <f t="shared" ref="T12:T16" si="14">AVERAGE(Q13:S13)</f>
+        <f t="shared" ref="T13:T16" si="14">AVERAGE(Q13:S13)</f>
         <v>19.833333333333332</v>
       </c>
       <c r="U13">
@@ -12056,11 +12056,11 @@
         <v>1.1252571722516165</v>
       </c>
       <c r="AC13">
-        <f t="shared" ref="AC12:AC16" si="15">MIN(Q13:S13)</f>
+        <f t="shared" ref="AC13:AC16" si="15">MIN(Q13:S13)</f>
         <v>12</v>
       </c>
       <c r="AD13">
-        <f t="shared" ref="AD12:AD16" si="16">(T13-AC13)</f>
+        <f t="shared" ref="AD13:AD16" si="16">(T13-AC13)</f>
         <v>7.8333333333333321</v>
       </c>
       <c r="AE13">

--- a/DataAnalysis/LF/0.05/Results.xlsx
+++ b/DataAnalysis/LF/0.05/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LF\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E56454D-D44E-4F2F-8F68-70983CB2E213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE11428-08F8-47B4-A0CF-B34F2CDD584D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="72">
   <si>
     <t>Dati originali</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>ep=0.1</t>
+  </si>
+  <si>
+    <t>try3</t>
   </si>
 </sst>
 </file>
@@ -582,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -828,366 +831,401 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11">
+        <v>17.666666666666668</v>
+      </c>
+      <c r="H11">
+        <v>2.3629078131263004</v>
+      </c>
+      <c r="I11">
+        <v>12.333333333333334</v>
+      </c>
+      <c r="J11">
+        <v>2.5166114784235849</v>
+      </c>
+      <c r="K11">
+        <v>29.166666666666668</v>
+      </c>
+      <c r="L11">
+        <v>5.2993710318615417</v>
+      </c>
+      <c r="M11">
+        <v>19.722222222222225</v>
+      </c>
+      <c r="N11">
+        <v>0.41943524640393165</v>
+      </c>
+      <c r="O11">
+        <v>7.3888888888888893</v>
+      </c>
+      <c r="P11">
+        <v>2.7504208432192381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12">
-        <v>22.15</v>
-      </c>
-      <c r="H12">
-        <v>1.8566696588844833</v>
-      </c>
-      <c r="I12">
-        <v>15</v>
-      </c>
-      <c r="J12">
-        <v>1.986062547968831</v>
-      </c>
-      <c r="K12">
-        <v>30.5</v>
-      </c>
-      <c r="L12">
-        <v>2.8674417556808756</v>
-      </c>
-      <c r="M12">
-        <v>22.549999999999997</v>
-      </c>
-      <c r="N12">
-        <v>1.0454191669220056</v>
-      </c>
-      <c r="O12">
-        <v>7.5500000000000016</v>
-      </c>
-      <c r="P12">
-        <v>2.3014354082336492</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>22.15</v>
+      </c>
+      <c r="H13">
+        <v>1.8566696588844833</v>
+      </c>
+      <c r="I13">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <v>1.986062547968831</v>
+      </c>
+      <c r="K13">
+        <v>30.5</v>
+      </c>
+      <c r="L13">
+        <v>2.8674417556808756</v>
+      </c>
+      <c r="M13">
+        <v>22.549999999999997</v>
+      </c>
+      <c r="N13">
+        <v>1.0454191669220056</v>
+      </c>
+      <c r="O13">
+        <v>7.5500000000000016</v>
+      </c>
+      <c r="P13">
+        <v>2.3014354082336492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
         <v>2</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>21</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>19</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>2.2360679774997898</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>11.1875</v>
       </c>
-      <c r="J13">
+      <c r="J14">
         <v>2.2350695099449847</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>26.6875</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>3.0930509672028177</v>
       </c>
-      <c r="M13">
+      <c r="M14">
         <v>18.958333333333332</v>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>0.7955730688858863</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>7.7708333333333339</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>2.3936713848004882</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16">
-        <v>23.214285714285715</v>
-      </c>
-      <c r="H16">
-        <v>2.6435005651777832</v>
-      </c>
-      <c r="I16">
-        <v>11.071428571428571</v>
-      </c>
-      <c r="J16">
-        <v>1.336306209562119</v>
-      </c>
-      <c r="K16">
-        <v>35.642857142857146</v>
-      </c>
-      <c r="L16">
-        <v>4.5434411125112195</v>
-      </c>
-      <c r="M16">
-        <v>23.309523809523807</v>
-      </c>
-      <c r="N16">
-        <v>1.5257923607235448</v>
-      </c>
-      <c r="O16">
-        <v>12.238095238095239</v>
-      </c>
-      <c r="P16">
-        <v>2.088010622527662</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>17.833333333333332</v>
+        <v>23.214285714285715</v>
       </c>
       <c r="H17">
-        <v>3.125166662222457</v>
+        <v>2.6435005651777832</v>
       </c>
       <c r="I17">
-        <v>8.5833333333333339</v>
+        <v>11.071428571428571</v>
       </c>
       <c r="J17">
-        <v>1.2416387021459434</v>
+        <v>1.336306209562119</v>
       </c>
       <c r="K17">
-        <v>28.583333333333332</v>
+        <v>35.642857142857146</v>
       </c>
       <c r="L17">
-        <v>3.6799003609699281</v>
+        <v>4.5434411125112195</v>
       </c>
       <c r="M17">
-        <v>18.333333333333332</v>
+        <v>23.309523809523807</v>
       </c>
       <c r="N17">
-        <v>1.7763883459298975</v>
+        <v>1.5257923607235448</v>
       </c>
       <c r="O17">
-        <v>9.75</v>
+        <v>12.238095238095239</v>
       </c>
       <c r="P17">
-        <v>1.0632758605157719</v>
+        <v>2.088010622527662</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>17.833333333333332</v>
+      </c>
+      <c r="H18">
+        <v>3.125166662222457</v>
+      </c>
+      <c r="I18">
+        <v>8.5833333333333339</v>
+      </c>
+      <c r="J18">
+        <v>1.2416387021459434</v>
+      </c>
+      <c r="K18">
+        <v>28.583333333333332</v>
+      </c>
+      <c r="L18">
+        <v>3.6799003609699281</v>
+      </c>
+      <c r="M18">
+        <v>18.333333333333332</v>
+      </c>
+      <c r="N18">
+        <v>1.7763883459298975</v>
+      </c>
+      <c r="O18">
+        <v>9.75</v>
+      </c>
+      <c r="P18">
+        <v>1.0632758605157719</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
-        <v>18.75</v>
-      </c>
-      <c r="H19">
-        <v>1.7559422921421233</v>
-      </c>
-      <c r="I19">
-        <v>10.5</v>
-      </c>
-      <c r="J19">
-        <v>2.2730302828309759</v>
-      </c>
-      <c r="K19">
-        <v>27.125</v>
-      </c>
-      <c r="L19">
-        <v>1.9311050377094112</v>
-      </c>
-      <c r="M19">
-        <v>18.791666666666664</v>
-      </c>
-      <c r="N19">
-        <v>1.1252571722516165</v>
-      </c>
-      <c r="O19">
-        <v>8.2916666666666661</v>
-      </c>
-      <c r="P19">
-        <v>1.1970256348008435</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20">
+        <v>18.75</v>
+      </c>
+      <c r="H20">
+        <v>1.7559422921421233</v>
+      </c>
+      <c r="I20">
+        <v>10.5</v>
+      </c>
+      <c r="J20">
+        <v>2.2730302828309759</v>
+      </c>
+      <c r="K20">
+        <v>27.125</v>
+      </c>
+      <c r="L20">
+        <v>1.9311050377094112</v>
+      </c>
+      <c r="M20">
+        <v>18.791666666666664</v>
+      </c>
+      <c r="N20">
+        <v>1.1252571722516165</v>
+      </c>
+      <c r="O20">
+        <v>8.2916666666666661</v>
+      </c>
+      <c r="P20">
+        <v>1.1970256348008435</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E21" t="s">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
         <v>64</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>17.375</v>
       </c>
-      <c r="H21">
+      <c r="H22">
         <v>2.75</v>
       </c>
-      <c r="I21">
+      <c r="I22">
         <v>10.375</v>
       </c>
-      <c r="J21">
+      <c r="J22">
         <v>3.4490336810958131</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>28.625</v>
       </c>
-      <c r="L21">
+      <c r="L22">
         <v>3.0103986446980739</v>
       </c>
-      <c r="M21">
+      <c r="M22">
         <v>18.791666666666668</v>
       </c>
-      <c r="N21">
+      <c r="N22">
         <v>2.5725581734055121</v>
       </c>
-      <c r="O21">
+      <c r="O22">
         <v>8.4166666666666679</v>
       </c>
-      <c r="P21">
+      <c r="P22">
         <v>1.6583123951776941</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24">
-        <v>19.583333333333332</v>
-      </c>
-      <c r="H24">
-        <v>2.3540744819709287</v>
-      </c>
-      <c r="I24">
-        <v>13.916666666666666</v>
-      </c>
-      <c r="J24">
-        <v>2.5380438661825075</v>
-      </c>
-      <c r="K24">
-        <v>23</v>
-      </c>
-      <c r="L24">
-        <v>5.196152422706632</v>
-      </c>
-      <c r="M24">
-        <v>18.833333333333332</v>
-      </c>
-      <c r="N24">
-        <v>1.8737959096740264</v>
-      </c>
-      <c r="O24">
-        <v>4.916666666666667</v>
-      </c>
-      <c r="P24">
-        <v>2.1337239225770932</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G25">
-        <v>21.1</v>
+        <v>19.583333333333332</v>
       </c>
       <c r="H25">
-        <v>3.8307962618755846</v>
+        <v>2.3540744819709287</v>
       </c>
       <c r="I25">
-        <v>11.9</v>
+        <v>13.916666666666666</v>
       </c>
       <c r="J25">
-        <v>3.7316216314090598</v>
+        <v>2.5380438661825075</v>
       </c>
       <c r="K25">
-        <v>24.4</v>
+        <v>23</v>
       </c>
       <c r="L25">
-        <v>3.2093613071762355</v>
+        <v>5.196152422706632</v>
       </c>
       <c r="M25">
-        <v>19.133333333333333</v>
+        <v>18.833333333333332</v>
       </c>
       <c r="N25">
-        <v>1.8234582528810472</v>
+        <v>1.8737959096740264</v>
       </c>
       <c r="O25">
-        <v>7.2333333333333343</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="P25">
-        <v>3.1898275815473136</v>
+        <v>2.1337239225770932</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>21.1</v>
+      </c>
+      <c r="H26">
+        <v>3.8307962618755846</v>
+      </c>
+      <c r="I26">
+        <v>11.9</v>
+      </c>
+      <c r="J26">
+        <v>3.7316216314090598</v>
+      </c>
+      <c r="K26">
+        <v>24.4</v>
+      </c>
+      <c r="L26">
+        <v>3.2093613071762355</v>
+      </c>
+      <c r="M26">
+        <v>19.133333333333333</v>
+      </c>
+      <c r="N26">
+        <v>1.8234582528810472</v>
+      </c>
+      <c r="O26">
+        <v>7.2333333333333343</v>
+      </c>
+      <c r="P26">
+        <v>3.1898275815473136</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E28" t="s">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
         <v>64</v>
       </c>
-      <c r="G28">
+      <c r="G29">
         <v>17.5</v>
       </c>
-      <c r="H28">
+      <c r="H29">
         <v>4.2720018726587652</v>
       </c>
-      <c r="I28">
+      <c r="I29">
         <v>12.333333333333334</v>
       </c>
-      <c r="J28">
+      <c r="J29">
         <v>1.2583057392117918</v>
       </c>
-      <c r="K28">
+      <c r="K29">
         <v>25.666666666666668</v>
       </c>
-      <c r="L28">
+      <c r="L29">
         <v>5.7518113089124689</v>
       </c>
-      <c r="M28">
+      <c r="M29">
         <v>18.5</v>
       </c>
-      <c r="N28">
+      <c r="N29">
         <v>3.3706247360261101</v>
       </c>
-      <c r="O28">
+      <c r="O29">
         <v>6.166666666666667</v>
       </c>
-      <c r="P28">
+      <c r="P29">
         <v>2.3154073315749666</v>
       </c>
     </row>
@@ -5164,7 +5202,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -5517,6 +5555,237 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>10.333333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>90</v>
+      </c>
+      <c r="G9">
+        <v>95</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <v>85</v>
+      </c>
+      <c r="L9">
+        <v>75</v>
+      </c>
+      <c r="M9">
+        <v>25</v>
+      </c>
+      <c r="N9">
+        <v>43</v>
+      </c>
+      <c r="O9">
+        <v>57</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q8:Q11" si="6">AVERAGE(C9:D9)</f>
+        <v>15</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R8:R11" si="7">AVERAGE(H9:I9)</f>
+        <v>10</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S8:S11" si="8">AVERAGE(M9:N9)</f>
+        <v>34</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T8:T11" si="9">AVERAGE(Q9:S9)</f>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="U9">
+        <f>AVERAGE(Q9:Q12)</f>
+        <v>17.666666666666668</v>
+      </c>
+      <c r="V9">
+        <f>_xlfn.STDEV.S(Q9:Q12)</f>
+        <v>2.3629078131263004</v>
+      </c>
+      <c r="W9">
+        <f>AVERAGE(R9:R12)</f>
+        <v>12.333333333333334</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.STDEV.S(R9:R12)</f>
+        <v>2.5166114784235849</v>
+      </c>
+      <c r="Y9">
+        <f>AVERAGE(S9:S12)</f>
+        <v>29.166666666666668</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.STDEV.S(S9:S12)</f>
+        <v>5.2993710318615417</v>
+      </c>
+      <c r="AA9">
+        <f>AVERAGE(T9:T12)</f>
+        <v>19.722222222222225</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.STDEV.S(T9:T12)</f>
+        <v>0.41943524640393165</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC8:AC10" si="10">MIN(Q9:S9)</f>
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD8:AD10" si="11">T9-AC9</f>
+        <v>9.6666666666666679</v>
+      </c>
+      <c r="AE9">
+        <f>AVERAGE(AD9:AD12)</f>
+        <v>7.3888888888888893</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.STDEV.S(AD9:AD12)</f>
+        <v>2.7504208432192381</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>86</v>
+      </c>
+      <c r="G10">
+        <v>92</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>16</v>
+      </c>
+      <c r="J10">
+        <v>84</v>
+      </c>
+      <c r="L10">
+        <v>87</v>
+      </c>
+      <c r="M10">
+        <v>13</v>
+      </c>
+      <c r="N10">
+        <v>47</v>
+      </c>
+      <c r="O10">
+        <v>53</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>18.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="11"/>
+        <v>8.1666666666666679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>81</v>
+      </c>
+      <c r="C11">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>80</v>
+      </c>
+      <c r="G11">
+        <v>91</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>21</v>
+      </c>
+      <c r="J11">
+        <v>79</v>
+      </c>
+      <c r="L11">
+        <v>81</v>
+      </c>
+      <c r="M11">
+        <v>19</v>
+      </c>
+      <c r="N11">
+        <v>28</v>
+      </c>
+      <c r="O11">
+        <v>72</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>19.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>23.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" ref="AC11" si="12">MIN(Q11:S11)</f>
+        <v>15</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" ref="AD11" si="13">T11-AC11</f>
+        <v>4.3333333333333321</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/LF/0.05/Results.xlsx
+++ b/DataAnalysis/LF/0.05/Results.xlsx
@@ -1,35 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LF\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE11428-08F8-47B4-A0CF-B34F2CDD584D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC78586D-DEDB-4108-B364-90DFBBFF50A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId6"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId7"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId8"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId9"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId11"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId12"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId13"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId15"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId16"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId17"/>
+    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId2"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId4"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId8"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId9"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId10"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId11"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="73">
   <si>
     <t>Dati originali</t>
   </si>
@@ -268,6 +269,9 @@
   </si>
   <si>
     <t>try3</t>
+  </si>
+  <si>
+    <t>trt3</t>
   </si>
 </sst>
 </file>
@@ -585,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1067,166 +1071,309 @@
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21">
+        <v>20.833333333333332</v>
+      </c>
+      <c r="H21">
+        <v>3.0138568866708604</v>
+      </c>
+      <c r="I21">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="J21">
+        <v>1.5275252316519499</v>
+      </c>
+      <c r="K21">
+        <v>30.666666666666668</v>
+      </c>
+      <c r="L21">
+        <v>3.0550504633038935</v>
+      </c>
+      <c r="M21">
+        <v>20.388888888888889</v>
+      </c>
+      <c r="N21">
+        <v>1.9883922409081429</v>
+      </c>
+      <c r="O21">
+        <v>10.722222222222223</v>
+      </c>
+      <c r="P21">
+        <v>2.4286103327104773</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E22" t="s">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
         <v>64</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>17.375</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>2.75</v>
       </c>
-      <c r="I22">
+      <c r="I23">
         <v>10.375</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>3.4490336810958131</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>28.625</v>
       </c>
-      <c r="L22">
+      <c r="L23">
         <v>3.0103986446980739</v>
       </c>
-      <c r="M22">
+      <c r="M23">
         <v>18.791666666666668</v>
       </c>
-      <c r="N22">
+      <c r="N23">
         <v>2.5725581734055121</v>
       </c>
-      <c r="O22">
+      <c r="O23">
         <v>8.4166666666666679</v>
       </c>
-      <c r="P22">
+      <c r="P23">
         <v>1.6583123951776941</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24">
+        <v>17.5</v>
+      </c>
+      <c r="H24">
+        <v>2.598076211353316</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <v>2.179449471770337</v>
+      </c>
+      <c r="K24">
+        <v>30.333333333333332</v>
+      </c>
+      <c r="L24">
+        <v>2.8431203515386634</v>
+      </c>
+      <c r="M24">
+        <v>19.277777777777775</v>
+      </c>
+      <c r="N24">
+        <v>1.8282758524338136</v>
+      </c>
+      <c r="O24">
+        <v>9.2777777777777768</v>
+      </c>
+      <c r="P24">
+        <v>2.219442706159791</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>19.583333333333332</v>
-      </c>
-      <c r="H25">
-        <v>2.3540744819709287</v>
-      </c>
-      <c r="I25">
-        <v>13.916666666666666</v>
-      </c>
-      <c r="J25">
-        <v>2.5380438661825075</v>
-      </c>
-      <c r="K25">
-        <v>23</v>
-      </c>
-      <c r="L25">
-        <v>5.196152422706632</v>
-      </c>
-      <c r="M25">
-        <v>18.833333333333332</v>
-      </c>
-      <c r="N25">
-        <v>1.8737959096740264</v>
-      </c>
-      <c r="O25">
-        <v>4.916666666666667</v>
-      </c>
-      <c r="P25">
-        <v>2.1337239225770932</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26">
-        <v>21.1</v>
-      </c>
-      <c r="H26">
-        <v>3.8307962618755846</v>
-      </c>
-      <c r="I26">
-        <v>11.9</v>
-      </c>
-      <c r="J26">
-        <v>3.7316216314090598</v>
-      </c>
-      <c r="K26">
-        <v>24.4</v>
-      </c>
-      <c r="L26">
-        <v>3.2093613071762355</v>
-      </c>
-      <c r="M26">
-        <v>19.133333333333333</v>
-      </c>
-      <c r="N26">
-        <v>1.8234582528810472</v>
-      </c>
-      <c r="O26">
-        <v>7.2333333333333343</v>
-      </c>
-      <c r="P26">
-        <v>3.1898275815473136</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>19.583333333333332</v>
+      </c>
+      <c r="H27">
+        <v>2.3540744819709287</v>
+      </c>
+      <c r="I27">
+        <v>13.916666666666666</v>
+      </c>
+      <c r="J27">
+        <v>2.5380438661825075</v>
+      </c>
+      <c r="K27">
+        <v>23</v>
+      </c>
+      <c r="L27">
+        <v>5.196152422706632</v>
+      </c>
+      <c r="M27">
+        <v>18.833333333333332</v>
+      </c>
+      <c r="N27">
+        <v>1.8737959096740264</v>
+      </c>
+      <c r="O27">
+        <v>4.916666666666667</v>
+      </c>
+      <c r="P27">
+        <v>2.1337239225770932</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>21.1</v>
+      </c>
+      <c r="H28">
+        <v>3.8307962618755846</v>
+      </c>
+      <c r="I28">
+        <v>11.9</v>
+      </c>
+      <c r="J28">
+        <v>3.7316216314090598</v>
+      </c>
+      <c r="K28">
+        <v>24.4</v>
+      </c>
+      <c r="L28">
+        <v>3.2093613071762355</v>
+      </c>
+      <c r="M28">
+        <v>19.133333333333333</v>
+      </c>
+      <c r="N28">
+        <v>1.8234582528810472</v>
+      </c>
+      <c r="O28">
+        <v>7.2333333333333343</v>
+      </c>
+      <c r="P28">
+        <v>3.1898275815473136</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30">
+        <v>14.833333333333334</v>
+      </c>
+      <c r="H30">
+        <v>1.2583057392117918</v>
+      </c>
+      <c r="I30">
+        <v>10.166666666666666</v>
+      </c>
+      <c r="J30">
+        <v>0.28867513459481292</v>
+      </c>
+      <c r="K30">
+        <v>21.5</v>
+      </c>
+      <c r="L30">
+        <v>3.5</v>
+      </c>
+      <c r="M30">
+        <v>15.5</v>
+      </c>
+      <c r="N30">
+        <v>1.0408329997330656</v>
+      </c>
+      <c r="O30">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="P30">
+        <v>0.8660254037844386</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E29" t="s">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
         <v>64</v>
       </c>
-      <c r="G29">
+      <c r="G32">
         <v>17.5</v>
       </c>
-      <c r="H29">
+      <c r="H32">
         <v>4.2720018726587652</v>
       </c>
-      <c r="I29">
+      <c r="I32">
         <v>12.333333333333334</v>
       </c>
-      <c r="J29">
+      <c r="J32">
         <v>1.2583057392117918</v>
       </c>
-      <c r="K29">
+      <c r="K32">
         <v>25.666666666666668</v>
       </c>
-      <c r="L29">
+      <c r="L32">
         <v>5.7518113089124689</v>
       </c>
-      <c r="M29">
+      <c r="M32">
         <v>18.5</v>
       </c>
-      <c r="N29">
+      <c r="N32">
         <v>3.3706247360261101</v>
       </c>
-      <c r="O29">
+      <c r="O32">
         <v>6.166666666666667</v>
       </c>
-      <c r="P29">
+      <c r="P32">
         <v>2.3154073315749666</v>
+      </c>
+    </row>
+    <row r="33" spans="6:16" x14ac:dyDescent="0.3">
+      <c r="F33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33">
+        <v>20</v>
+      </c>
+      <c r="H33">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="I33">
+        <v>8.75</v>
+      </c>
+      <c r="J33">
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="K33">
+        <v>23</v>
+      </c>
+      <c r="L33">
+        <v>4.2426406871192848</v>
+      </c>
+      <c r="M33">
+        <v>17.25</v>
+      </c>
+      <c r="N33">
+        <v>1.2963624321753389</v>
+      </c>
+      <c r="O33">
+        <v>8.5</v>
+      </c>
+      <c r="P33">
+        <v>0.94280904158206502</v>
       </c>
     </row>
   </sheetData>
@@ -1236,6 +1383,495 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
+  <dimension ref="A2:AF9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>88</v>
+      </c>
+      <c r="G4">
+        <v>99</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>86</v>
+      </c>
+      <c r="L4">
+        <v>80</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>33</v>
+      </c>
+      <c r="O4">
+        <v>67</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>7.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>26.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q9)</f>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q9)</f>
+        <v>3.125166662222457</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R9)</f>
+        <v>8.5833333333333339</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R9)</f>
+        <v>1.2416387021459434</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S9)</f>
+        <v>28.583333333333332</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S9)</f>
+        <v>3.6799003609699281</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T9)</f>
+        <v>18.333333333333332</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T9)</f>
+        <v>1.7763883459298975</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>7.5</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD9)</f>
+        <v>9.75</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD9)</f>
+        <v>1.0632758605157719</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>70</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="G5">
+        <v>92</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>88</v>
+      </c>
+      <c r="L5">
+        <v>85</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>39</v>
+      </c>
+      <c r="O5">
+        <v>61</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
+        <v>23.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
+        <v>10</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
+        <v>27</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD9" si="5">T5-AC5</f>
+        <v>10.166666666666668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>82</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>87</v>
+      </c>
+      <c r="G6">
+        <v>96</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>89</v>
+      </c>
+      <c r="L6">
+        <v>75</v>
+      </c>
+      <c r="M6">
+        <v>25</v>
+      </c>
+      <c r="N6">
+        <v>40</v>
+      </c>
+      <c r="O6">
+        <v>60</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>18.5</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>82</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>80</v>
+      </c>
+      <c r="G7">
+        <v>93</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>89</v>
+      </c>
+      <c r="L7">
+        <v>76</v>
+      </c>
+      <c r="M7">
+        <v>24</v>
+      </c>
+      <c r="N7">
+        <v>39</v>
+      </c>
+      <c r="O7">
+        <v>61</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>31.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>10.833333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>79</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>86</v>
+      </c>
+      <c r="G8">
+        <v>95</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>90</v>
+      </c>
+      <c r="L8">
+        <v>86</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+      <c r="N8">
+        <v>32</v>
+      </c>
+      <c r="O8">
+        <v>68</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>78</v>
+      </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9">
+        <v>89</v>
+      </c>
+      <c r="G9">
+        <v>93</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>13</v>
+      </c>
+      <c r="J9">
+        <v>87</v>
+      </c>
+      <c r="L9">
+        <v>76</v>
+      </c>
+      <c r="M9">
+        <v>24</v>
+      </c>
+      <c r="N9">
+        <v>38</v>
+      </c>
+      <c r="O9">
+        <v>62</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>9.1666666666666679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
   <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1783,7 +2419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AN99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4468,7 +5104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5200,7 +5836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5600,19 +6236,19 @@
         <v>57</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q8:Q11" si="6">AVERAGE(C9:D9)</f>
+        <f t="shared" ref="Q9:Q11" si="6">AVERAGE(C9:D9)</f>
         <v>15</v>
       </c>
       <c r="R9">
-        <f t="shared" ref="R8:R11" si="7">AVERAGE(H9:I9)</f>
+        <f t="shared" ref="R9:R11" si="7">AVERAGE(H9:I9)</f>
         <v>10</v>
       </c>
       <c r="S9">
-        <f t="shared" ref="S8:S11" si="8">AVERAGE(M9:N9)</f>
+        <f t="shared" ref="S9:S11" si="8">AVERAGE(M9:N9)</f>
         <v>34</v>
       </c>
       <c r="T9">
-        <f t="shared" ref="T8:T11" si="9">AVERAGE(Q9:S9)</f>
+        <f t="shared" ref="T9:T11" si="9">AVERAGE(Q9:S9)</f>
         <v>19.666666666666668</v>
       </c>
       <c r="U9">
@@ -5648,11 +6284,11 @@
         <v>0.41943524640393165</v>
       </c>
       <c r="AC9">
-        <f t="shared" ref="AC8:AC10" si="10">MIN(Q9:S9)</f>
+        <f t="shared" ref="AC9:AC10" si="10">MIN(Q9:S9)</f>
         <v>10</v>
       </c>
       <c r="AD9">
-        <f t="shared" ref="AD8:AD10" si="11">T9-AC9</f>
+        <f t="shared" ref="AD9:AD10" si="11">T9-AC9</f>
         <v>9.6666666666666679</v>
       </c>
       <c r="AE9">
@@ -5793,7 +6429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AF36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6793,7 +7429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AF36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7794,7 +8430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10330,7 +10966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10632,527 +11268,284 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7986D54-7707-40F4-AFC2-8FFB01A635DF}">
+  <dimension ref="B1:AF4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" t="s">
+    <row r="1" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R1" t="s">
         <v>13</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U1" t="s">
         <v>52</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V1" t="s">
         <v>45</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W1" t="s">
         <v>53</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X1" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y1" t="s">
         <v>54</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="Z1" t="s">
         <v>47</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA1" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB1" t="s">
         <v>17</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC1" t="s">
         <v>18</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD1" t="s">
         <v>15</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE1" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" t="s">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>86</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>87</v>
+      </c>
+      <c r="G2">
+        <v>96</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>83</v>
+      </c>
+      <c r="L2">
+        <v>85</v>
+      </c>
+      <c r="M2">
+        <v>15</v>
+      </c>
+      <c r="N2">
+        <v>35</v>
+      </c>
+      <c r="O2">
+        <v>65</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2" si="0">AVERAGE(C2,D2)</f>
+        <v>13.5</v>
+      </c>
+      <c r="R2">
+        <f t="shared" ref="R2" si="1">AVERAGE(H2,I2)</f>
+        <v>10.5</v>
+      </c>
+      <c r="S2">
+        <f t="shared" ref="S2" si="2">AVERAGE(M2,N2)</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="T2">
+        <f t="shared" ref="T2" si="3">AVERAGE(Q2:S2)</f>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="U2">
+        <f>AVERAGE(Q2:Q5)</f>
+        <v>14.833333333333334</v>
+      </c>
+      <c r="V2">
+        <f>_xlfn.STDEV.S(Q2:Q5)</f>
+        <v>1.2583057392117918</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGE(R2:R5)</f>
+        <v>10.166666666666666</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.STDEV.S(R2:R5)</f>
+        <v>0.28867513459481292</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGE(S2:S5)</f>
+        <v>21.5</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.STDEV.S(S2:S5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="AA2">
+        <f>AVERAGE(T2:T5)</f>
+        <v>15.5</v>
+      </c>
+      <c r="AB2">
+        <f>_xlfn.STDEV.S(T2:T5)</f>
+        <v>1.0408329997330656</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" ref="AC2" si="4">MIN(Q2:S2)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AD2">
+        <f t="shared" ref="AD2" si="5">(T2-AC2)</f>
+        <v>5.8333333333333321</v>
+      </c>
+      <c r="AE2">
+        <f>AVERAGE(AD2:AD5)</f>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="AF2">
+        <f>_xlfn.STDEV.S(AD2:AD5)</f>
+        <v>0.8660254037844386</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>87</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>19</v>
+      </c>
+      <c r="E3">
+        <v>81</v>
+      </c>
+      <c r="G3">
+        <v>95</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>15</v>
+      </c>
+      <c r="J3">
+        <v>85</v>
+      </c>
+      <c r="L3">
+        <v>91</v>
+      </c>
+      <c r="M3">
+        <v>9</v>
+      </c>
+      <c r="N3">
+        <v>34</v>
+      </c>
+      <c r="O3">
+        <v>66</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q4" si="6">AVERAGE(C3,D3)</f>
+        <v>16</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R4" si="7">AVERAGE(H3,I3)</f>
+        <v>10</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S4" si="8">AVERAGE(M3,N3)</f>
+        <v>21.5</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T4" si="9">AVERAGE(Q3:S3)</f>
+        <v>15.833333333333334</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" ref="AC3:AC4" si="10">MIN(Q3:S3)</f>
+        <v>10</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" ref="AD3:AD4" si="11">(T3-AC3)</f>
+        <v>5.8333333333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>86</v>
+      </c>
+      <c r="G4">
+        <v>92</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>88</v>
+      </c>
+      <c r="L4">
+        <v>85</v>
+      </c>
+      <c r="M4">
+        <v>15</v>
+      </c>
+      <c r="N4">
+        <v>21</v>
+      </c>
+      <c r="O4">
+        <v>79</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4">
-        <v>91</v>
-      </c>
-      <c r="G4">
-        <v>98</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>86</v>
-      </c>
-      <c r="L4">
-        <v>78</v>
-      </c>
-      <c r="M4">
-        <v>22</v>
-      </c>
-      <c r="N4">
-        <v>31</v>
-      </c>
-      <c r="O4">
-        <v>69</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>13.5</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>8</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>26.5</v>
-      </c>
       <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>16</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q7)</f>
-        <v>17.375</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q7)</f>
-        <v>2.75</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R7)</f>
-        <v>10.375</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R7)</f>
-        <v>3.4490336810958131</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S7)</f>
-        <v>28.625</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S7)</f>
-        <v>3.0103986446980739</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T7)</f>
-        <v>18.791666666666668</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T7)</f>
-        <v>2.5725581734055121</v>
+        <f t="shared" si="9"/>
+        <v>14.333333333333334</v>
       </c>
       <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <f>(T4-AC4)</f>
-        <v>8</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD7)</f>
-        <v>8.4166666666666679</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD7)</f>
-        <v>1.6583123951776941</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>81</v>
-      </c>
-      <c r="C5">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>83</v>
-      </c>
-      <c r="G5">
-        <v>95</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-      <c r="J5">
-        <v>87</v>
-      </c>
-      <c r="L5">
-        <v>79</v>
-      </c>
-      <c r="M5">
-        <v>21</v>
-      </c>
-      <c r="N5">
-        <v>31</v>
-      </c>
-      <c r="O5">
-        <v>69</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5" si="0">AVERAGE(C5,D5)</f>
-        <v>18</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5" si="1">AVERAGE(H5,I5)</f>
-        <v>9</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5" si="2">AVERAGE(M5,N5)</f>
-        <v>26</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5" si="3">AVERAGE(Q5:S5)</f>
-        <v>17.666666666666668</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5" si="4">MIN(Q5:S5)</f>
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD7" si="5">(T5-AC5)</f>
-        <v>8.6666666666666679</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>69</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>91</v>
-      </c>
-      <c r="G6">
-        <v>92</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>90</v>
-      </c>
-      <c r="L6">
-        <v>76</v>
-      </c>
-      <c r="M6">
-        <v>24</v>
-      </c>
-      <c r="N6">
-        <v>35</v>
-      </c>
-      <c r="O6">
-        <v>65</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" ref="Q6:Q7" si="6">AVERAGE(C6,D6)</f>
-        <v>20</v>
-      </c>
-      <c r="R6">
-        <f t="shared" ref="R6:R7" si="7">AVERAGE(H6,I6)</f>
-        <v>9</v>
-      </c>
-      <c r="S6">
-        <f t="shared" ref="S6:S7" si="8">AVERAGE(M6,N6)</f>
-        <v>29.5</v>
-      </c>
-      <c r="T6">
-        <f t="shared" ref="T6:T7" si="9">AVERAGE(Q6:S6)</f>
-        <v>19.5</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" ref="AC6:AC7" si="10">MIN(Q6:S6)</f>
-        <v>9</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <v>77</v>
-      </c>
-      <c r="C7">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7">
-        <v>87</v>
-      </c>
-      <c r="G7">
-        <v>92</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>23</v>
-      </c>
-      <c r="J7">
-        <v>77</v>
-      </c>
-      <c r="L7">
-        <v>71</v>
-      </c>
-      <c r="M7">
-        <v>29</v>
-      </c>
-      <c r="N7">
-        <v>36</v>
-      </c>
-      <c r="O7">
-        <v>64</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="6"/>
-        <v>18</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="7"/>
-        <v>15.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="8"/>
-        <v>32.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="9"/>
-        <v>22</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="10"/>
-        <v>15.5</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>64</v>
-      </c>
-      <c r="C9">
-        <v>36</v>
-      </c>
-      <c r="D9">
-        <v>13</v>
-      </c>
-      <c r="E9">
-        <v>87</v>
-      </c>
-      <c r="G9">
-        <v>92</v>
-      </c>
-      <c r="H9">
-        <v>8</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <v>89</v>
-      </c>
-      <c r="L9">
-        <v>93</v>
-      </c>
-      <c r="M9">
-        <v>7</v>
-      </c>
-      <c r="N9">
-        <v>46</v>
-      </c>
-      <c r="O9">
-        <v>54</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" ref="Q9:Q10" si="11">AVERAGE(C9,D9)</f>
-        <v>24.5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" ref="R9:R10" si="12">AVERAGE(H9,I9)</f>
-        <v>9.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" ref="S9:S10" si="13">AVERAGE(M9,N9)</f>
-        <v>26.5</v>
-      </c>
-      <c r="T9">
-        <f t="shared" ref="T9:T10" si="14">AVERAGE(Q9:S9)</f>
-        <v>20.166666666666668</v>
-      </c>
-      <c r="U9">
-        <f>AVERAGE(Q9:Q12)</f>
-        <v>22.25</v>
-      </c>
-      <c r="V9">
-        <f>_xlfn.STDEV.S(Q9:Q12)</f>
-        <v>3.1819805153394638</v>
-      </c>
-      <c r="W9">
-        <f>AVERAGE(R9:R12)</f>
-        <v>10.75</v>
-      </c>
-      <c r="X9">
-        <f>_xlfn.STDEV.S(R9:R12)</f>
-        <v>1.7677669529663689</v>
-      </c>
-      <c r="Y9">
-        <f>AVERAGE(S9:S12)</f>
-        <v>27</v>
-      </c>
-      <c r="Z9">
-        <f>_xlfn.STDEV.S(S9:S12)</f>
-        <v>0.70710678118654757</v>
-      </c>
-      <c r="AA9">
-        <f>AVERAGE(T9:T12)</f>
-        <v>20</v>
-      </c>
-      <c r="AB9">
-        <f>_xlfn.STDEV.S(T9:T12)</f>
-        <v>0.2357022603955175</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" ref="AC9:AC10" si="15">MIN(Q9:S9)</f>
-        <v>9.5</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" ref="AD9:AD10" si="16">(T9-AC9)</f>
-        <v>10.666666666666668</v>
-      </c>
-      <c r="AE9">
-        <f>AVERAGE(AD9:AD12)</f>
-        <v>9.25</v>
-      </c>
-      <c r="AF9">
-        <f>_xlfn.STDEV.S(AD9:AD12)</f>
-        <v>2.0034692133618837</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>82</v>
-      </c>
-      <c r="C10">
-        <v>18</v>
-      </c>
-      <c r="D10">
-        <v>22</v>
-      </c>
-      <c r="E10">
-        <v>78</v>
-      </c>
-      <c r="G10">
-        <v>89</v>
-      </c>
-      <c r="H10">
-        <v>11</v>
-      </c>
-      <c r="I10">
-        <v>13</v>
-      </c>
-      <c r="J10">
-        <v>87</v>
-      </c>
-      <c r="L10">
-        <v>75</v>
-      </c>
-      <c r="M10">
-        <v>25</v>
-      </c>
-      <c r="N10">
-        <v>30</v>
-      </c>
-      <c r="O10">
-        <v>70</v>
-      </c>
-      <c r="Q10">
         <f t="shared" si="11"/>
-        <v>20</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="12"/>
-        <v>12</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="13"/>
-        <v>27.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="14"/>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="AC10">
-        <f t="shared" si="15"/>
-        <v>12</v>
-      </c>
-      <c r="AD10">
-        <f t="shared" si="16"/>
-        <v>7.8333333333333321</v>
+        <v>4.3333333333333339</v>
       </c>
     </row>
   </sheetData>
@@ -11161,6 +11554,766 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
+  <dimension ref="A2:AF17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>91</v>
+      </c>
+      <c r="G4">
+        <v>98</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>86</v>
+      </c>
+      <c r="L4">
+        <v>78</v>
+      </c>
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4">
+        <v>31</v>
+      </c>
+      <c r="O4">
+        <v>69</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>13.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>8</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>26.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>16</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q7)</f>
+        <v>17.375</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q7)</f>
+        <v>2.75</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R7)</f>
+        <v>10.375</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R7)</f>
+        <v>3.4490336810958131</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S7)</f>
+        <v>28.625</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S7)</f>
+        <v>3.0103986446980739</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T7)</f>
+        <v>18.791666666666668</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T7)</f>
+        <v>2.5725581734055121</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>8</v>
+      </c>
+      <c r="AD4">
+        <f>(T4-AC4)</f>
+        <v>8</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD7)</f>
+        <v>8.4166666666666679</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD7)</f>
+        <v>1.6583123951776941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="G5">
+        <v>95</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>87</v>
+      </c>
+      <c r="L5">
+        <v>79</v>
+      </c>
+      <c r="M5">
+        <v>21</v>
+      </c>
+      <c r="N5">
+        <v>31</v>
+      </c>
+      <c r="O5">
+        <v>69</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5" si="0">AVERAGE(C5,D5)</f>
+        <v>18</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5" si="1">AVERAGE(H5,I5)</f>
+        <v>9</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5" si="2">AVERAGE(M5,N5)</f>
+        <v>26</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5" si="3">AVERAGE(Q5:S5)</f>
+        <v>17.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5" si="4">MIN(Q5:S5)</f>
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD7" si="5">(T5-AC5)</f>
+        <v>8.6666666666666679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>69</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>91</v>
+      </c>
+      <c r="G6">
+        <v>92</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>90</v>
+      </c>
+      <c r="L6">
+        <v>76</v>
+      </c>
+      <c r="M6">
+        <v>24</v>
+      </c>
+      <c r="N6">
+        <v>35</v>
+      </c>
+      <c r="O6">
+        <v>65</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" ref="Q6:Q7" si="6">AVERAGE(C6,D6)</f>
+        <v>20</v>
+      </c>
+      <c r="R6">
+        <f t="shared" ref="R6:R7" si="7">AVERAGE(H6,I6)</f>
+        <v>9</v>
+      </c>
+      <c r="S6">
+        <f t="shared" ref="S6:S7" si="8">AVERAGE(M6,N6)</f>
+        <v>29.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" ref="T6:T7" si="9">AVERAGE(Q6:S6)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" ref="AC6:AC7" si="10">MIN(Q6:S6)</f>
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>77</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>87</v>
+      </c>
+      <c r="G7">
+        <v>92</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>77</v>
+      </c>
+      <c r="L7">
+        <v>71</v>
+      </c>
+      <c r="M7">
+        <v>29</v>
+      </c>
+      <c r="N7">
+        <v>36</v>
+      </c>
+      <c r="O7">
+        <v>64</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="7"/>
+        <v>15.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="8"/>
+        <v>32.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="9"/>
+        <v>22</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="10"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>64</v>
+      </c>
+      <c r="C9">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>87</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>11</v>
+      </c>
+      <c r="J9">
+        <v>89</v>
+      </c>
+      <c r="L9">
+        <v>93</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <v>46</v>
+      </c>
+      <c r="O9">
+        <v>54</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q9:Q10" si="11">AVERAGE(C9,D9)</f>
+        <v>24.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R9:R10" si="12">AVERAGE(H9,I9)</f>
+        <v>9.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S9:S10" si="13">AVERAGE(M9,N9)</f>
+        <v>26.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T9:T10" si="14">AVERAGE(Q9:S9)</f>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U9">
+        <f>AVERAGE(Q9:Q12)</f>
+        <v>22.25</v>
+      </c>
+      <c r="V9">
+        <f>_xlfn.STDEV.S(Q9:Q12)</f>
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="W9">
+        <f>AVERAGE(R9:R12)</f>
+        <v>10.75</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.STDEV.S(R9:R12)</f>
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="Y9">
+        <f>AVERAGE(S9:S12)</f>
+        <v>27</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.STDEV.S(S9:S12)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="AA9">
+        <f>AVERAGE(T9:T12)</f>
+        <v>20</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.STDEV.S(T9:T12)</f>
+        <v>0.2357022603955175</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC9:AC10" si="15">MIN(Q9:S9)</f>
+        <v>9.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD9:AD10" si="16">(T9-AC9)</f>
+        <v>10.666666666666668</v>
+      </c>
+      <c r="AE9">
+        <f>AVERAGE(AD9:AD12)</f>
+        <v>9.25</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.STDEV.S(AD9:AD12)</f>
+        <v>2.0034692133618837</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>22</v>
+      </c>
+      <c r="E10">
+        <v>78</v>
+      </c>
+      <c r="G10">
+        <v>89</v>
+      </c>
+      <c r="H10">
+        <v>11</v>
+      </c>
+      <c r="I10">
+        <v>13</v>
+      </c>
+      <c r="J10">
+        <v>87</v>
+      </c>
+      <c r="L10">
+        <v>75</v>
+      </c>
+      <c r="M10">
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <v>30</v>
+      </c>
+      <c r="O10">
+        <v>70</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="13"/>
+        <v>27.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="14"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="16"/>
+        <v>7.8333333333333321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>80</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>18</v>
+      </c>
+      <c r="E15">
+        <v>82</v>
+      </c>
+      <c r="G15">
+        <v>94</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>19</v>
+      </c>
+      <c r="J15">
+        <v>81</v>
+      </c>
+      <c r="L15">
+        <v>84</v>
+      </c>
+      <c r="M15">
+        <v>16</v>
+      </c>
+      <c r="N15">
+        <v>43</v>
+      </c>
+      <c r="O15">
+        <v>57</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" ref="Q11:Q17" si="17">AVERAGE(C15,D15)</f>
+        <v>19</v>
+      </c>
+      <c r="R15">
+        <f t="shared" ref="R11:R17" si="18">AVERAGE(H15,I15)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" ref="S11:S17" si="19">AVERAGE(M15,N15)</f>
+        <v>29.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" ref="T11:T17" si="20">AVERAGE(Q15:S15)</f>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U15">
+        <f>AVERAGE(Q15:Q18)</f>
+        <v>17.5</v>
+      </c>
+      <c r="V15">
+        <f>_xlfn.STDEV.S(Q15:Q18)</f>
+        <v>2.598076211353316</v>
+      </c>
+      <c r="W15">
+        <f>AVERAGE(R15:R18)</f>
+        <v>10</v>
+      </c>
+      <c r="X15">
+        <f>_xlfn.STDEV.S(R15:R18)</f>
+        <v>2.179449471770337</v>
+      </c>
+      <c r="Y15">
+        <f>AVERAGE(S15:S18)</f>
+        <v>30.333333333333332</v>
+      </c>
+      <c r="Z15">
+        <f>_xlfn.STDEV.S(S15:S18)</f>
+        <v>2.8431203515386634</v>
+      </c>
+      <c r="AA15">
+        <f>AVERAGE(T15:T18)</f>
+        <v>19.277777777777775</v>
+      </c>
+      <c r="AB15">
+        <f>_xlfn.STDEV.S(T15:T18)</f>
+        <v>1.8282758524338136</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" ref="AC11:AC17" si="21">MIN(Q15:S15)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" ref="AD11:AD17" si="22">(T15-AC15)</f>
+        <v>7.8333333333333321</v>
+      </c>
+      <c r="AE15">
+        <f>AVERAGE(AD15:AD18)</f>
+        <v>9.2777777777777768</v>
+      </c>
+      <c r="AF15">
+        <f>_xlfn.STDEV.S(AD15:AD18)</f>
+        <v>2.219442706159791</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>88</v>
+      </c>
+      <c r="G16">
+        <v>90</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16">
+        <v>92</v>
+      </c>
+      <c r="L16">
+        <v>83</v>
+      </c>
+      <c r="M16">
+        <v>17</v>
+      </c>
+      <c r="N16">
+        <v>39</v>
+      </c>
+      <c r="O16">
+        <v>61</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="17"/>
+        <v>14.5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="19"/>
+        <v>28</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="20"/>
+        <v>17.166666666666668</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="22"/>
+        <v>8.1666666666666679</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>22</v>
+      </c>
+      <c r="E17">
+        <v>78</v>
+      </c>
+      <c r="G17">
+        <v>97</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>14</v>
+      </c>
+      <c r="J17">
+        <v>86</v>
+      </c>
+      <c r="L17">
+        <v>72</v>
+      </c>
+      <c r="M17">
+        <v>28</v>
+      </c>
+      <c r="N17">
+        <v>39</v>
+      </c>
+      <c r="O17">
+        <v>61</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="18"/>
+        <v>8.5</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="19"/>
+        <v>33.5</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="20"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="21"/>
+        <v>8.5</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="22"/>
+        <v>11.833333333333332</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11326,9 +12479,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11626,905 +12779,173 @@
         <v>23</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" t="s">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="E12">
+        <v>82</v>
+      </c>
+      <c r="G12">
+        <v>97</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>15</v>
+      </c>
+      <c r="J12">
+        <v>85</v>
+      </c>
+      <c r="L12">
+        <v>92</v>
+      </c>
+      <c r="M12">
+        <v>8</v>
+      </c>
+      <c r="N12">
+        <v>44</v>
+      </c>
+      <c r="O12">
+        <v>56</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q7:Q13" si="6">AVERAGE(C12:D12)</f>
+        <v>19.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R7:R13" si="7">AVERAGE(H12:I12)</f>
+        <v>9</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S7:S13" si="8">AVERAGE(M12:N12)</f>
+        <v>26</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T7:T13" si="9">AVERAGE(Q12:S12)</f>
+        <v>18.166666666666668</v>
+      </c>
+      <c r="U12">
+        <f>AVERAGE(Q12:Q14)</f>
+        <v>20</v>
+      </c>
+      <c r="V12">
+        <f>_xlfn.STDEV.S(Q12:Q14)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(R12:R15)</f>
+        <v>8.75</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(R12:R14)</f>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(S12:S14)</f>
+        <v>23</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(S12:S14)</f>
+        <v>4.2426406871192848</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(T12:T14)</f>
+        <v>17.25</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(T12:T14)</f>
+        <v>1.2963624321753389</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" ref="AC7:AC13" si="10">MIN(Q12:S12)</f>
+        <v>9</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" ref="AD7:AD13" si="11">T12-AC12</f>
+        <v>9.1666666666666679</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(AD12:AD14)</f>
+        <v>8.5</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(AD12:AD14)</f>
+        <v>0.94280904158206502</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>71</v>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13">
         <v>12</v>
       </c>
-      <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="E13">
+        <v>88</v>
+      </c>
+      <c r="G13">
+        <v>89</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>6</v>
+      </c>
+      <c r="J13">
+        <v>94</v>
+      </c>
+      <c r="L13">
+        <v>86</v>
+      </c>
+      <c r="M13">
         <v>14</v>
       </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>72</v>
-      </c>
-      <c r="C4">
-        <v>28</v>
-      </c>
-      <c r="D4">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>86</v>
-      </c>
-      <c r="G4">
-        <v>96</v>
-      </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>86</v>
-      </c>
-      <c r="L4">
-        <v>82</v>
-      </c>
-      <c r="M4">
-        <v>18</v>
-      </c>
-      <c r="N4">
-        <v>39</v>
-      </c>
-      <c r="O4">
-        <v>61</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>21</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>9</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>28.5</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>19.5</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q11)</f>
-        <v>19.5625</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q11)</f>
-        <v>3.2997564845216774</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R11)</f>
-        <v>8.8125</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R11)</f>
-        <v>2.0863074009907003</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S11)</f>
-        <v>27.4375</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S11)</f>
-        <v>1.2374368670764582</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T11)</f>
-        <v>18.604166666666668</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T11)</f>
-        <v>1.4473223771821069</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>9</v>
-      </c>
-      <c r="AD4">
-        <f>(T4-AC4)</f>
-        <v>10.5</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD11)</f>
-        <v>9.7916666666666661</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD11)</f>
-        <v>1.6250763107845259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>79</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>88</v>
-      </c>
-      <c r="G5">
-        <v>90</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-      <c r="J5">
-        <v>87</v>
-      </c>
-      <c r="L5">
-        <v>79</v>
-      </c>
-      <c r="M5">
-        <v>21</v>
-      </c>
-      <c r="N5">
-        <v>35</v>
-      </c>
-      <c r="O5">
-        <v>65</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5" si="0">AVERAGE(C5,D5)</f>
-        <v>16.5</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5" si="1">AVERAGE(H5,I5)</f>
-        <v>11.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5" si="2">AVERAGE(M5,N5)</f>
-        <v>28</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5" si="3">AVERAGE(Q5:S5)</f>
-        <v>18.666666666666668</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5" si="4">MIN(Q5:S5)</f>
-        <v>11.5</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD11" si="5">(T5-AC5)</f>
-        <v>7.1666666666666679</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>67</v>
-      </c>
-      <c r="C6">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>88</v>
-      </c>
-      <c r="G6">
-        <v>92</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>94</v>
-      </c>
-      <c r="L6">
-        <v>70</v>
-      </c>
-      <c r="M6">
-        <v>30</v>
-      </c>
-      <c r="N6">
-        <v>23</v>
-      </c>
-      <c r="O6">
-        <v>77</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" ref="Q6:Q11" si="6">AVERAGE(C6,D6)</f>
-        <v>22.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" ref="R6:R11" si="7">AVERAGE(H6,I6)</f>
-        <v>7</v>
-      </c>
-      <c r="S6">
-        <f t="shared" ref="S6:S11" si="8">AVERAGE(M6,N6)</f>
-        <v>26.5</v>
-      </c>
-      <c r="T6">
-        <f t="shared" ref="T6:T11" si="9">AVERAGE(Q6:S6)</f>
-        <v>18.666666666666668</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" ref="AC6:AC11" si="10">MIN(Q6:S6)</f>
-        <v>7</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>11.666666666666668</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <v>75</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>83</v>
-      </c>
-      <c r="G7">
-        <v>95</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-      <c r="L7">
-        <v>86</v>
-      </c>
-      <c r="M7">
-        <v>14</v>
-      </c>
-      <c r="N7">
-        <v>40</v>
-      </c>
-      <c r="O7">
-        <v>60</v>
-      </c>
-      <c r="Q7">
+      <c r="N13">
+        <v>26</v>
+      </c>
+      <c r="O13">
+        <v>74</v>
+      </c>
+      <c r="Q13">
         <f t="shared" si="6"/>
-        <v>21</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="7"/>
-        <v>7.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="8"/>
-        <v>27</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="9"/>
-        <v>18.5</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="10"/>
-        <v>7.5</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>82</v>
-      </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>86</v>
-      </c>
-      <c r="G8">
-        <v>97</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>9</v>
-      </c>
-      <c r="J8">
-        <v>91</v>
-      </c>
-      <c r="L8">
-        <v>83</v>
-      </c>
-      <c r="M8">
-        <v>17</v>
-      </c>
-      <c r="N8">
-        <v>42</v>
-      </c>
-      <c r="O8">
-        <v>58</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="6"/>
-        <v>16</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="8"/>
-        <v>29.5</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="9"/>
-        <v>17.166666666666668</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>11.166666666666668</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>89</v>
-      </c>
-      <c r="C9">
-        <v>11</v>
-      </c>
-      <c r="D9">
-        <v>19</v>
-      </c>
-      <c r="E9">
-        <v>81</v>
-      </c>
-      <c r="G9">
-        <v>97</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
-      <c r="I9">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>86</v>
-      </c>
-      <c r="L9">
-        <v>91</v>
-      </c>
-      <c r="M9">
-        <v>9</v>
-      </c>
-      <c r="N9">
-        <v>42</v>
-      </c>
-      <c r="O9">
-        <v>58</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="R9">
+        <v>20.5</v>
+      </c>
+      <c r="R13">
         <f t="shared" si="7"/>
         <v>8.5</v>
       </c>
-      <c r="S9">
+      <c r="S13">
         <f t="shared" si="8"/>
-        <v>25.5</v>
-      </c>
-      <c r="T9">
+        <v>20</v>
+      </c>
+      <c r="T13">
         <f t="shared" si="9"/>
         <v>16.333333333333332</v>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f t="shared" si="10"/>
         <v>8.5</v>
       </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
+      <c r="AD13">
+        <f t="shared" si="11"/>
         <v>7.8333333333333321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>67</v>
-      </c>
-      <c r="C10">
-        <v>33</v>
-      </c>
-      <c r="D10">
-        <v>15</v>
-      </c>
-      <c r="E10">
-        <v>85</v>
-      </c>
-      <c r="G10">
-        <v>93</v>
-      </c>
-      <c r="H10">
-        <v>7</v>
-      </c>
-      <c r="I10">
-        <v>17</v>
-      </c>
-      <c r="J10">
-        <v>83</v>
-      </c>
-      <c r="L10">
-        <v>81</v>
-      </c>
-      <c r="M10">
-        <v>19</v>
-      </c>
-      <c r="N10">
-        <v>36</v>
-      </c>
-      <c r="O10">
-        <v>64</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="6"/>
-        <v>24</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="7"/>
-        <v>12</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="8"/>
-        <v>27.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="9"/>
-        <v>21.166666666666668</v>
-      </c>
-      <c r="AC10">
-        <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="AD10">
-        <f t="shared" si="5"/>
-        <v>9.1666666666666679</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>69</v>
-      </c>
-      <c r="C11">
-        <v>31</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11">
-        <v>90</v>
-      </c>
-      <c r="G11">
-        <v>92</v>
-      </c>
-      <c r="H11">
-        <v>8</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <v>90</v>
-      </c>
-      <c r="L11">
-        <v>79</v>
-      </c>
-      <c r="M11">
-        <v>21</v>
-      </c>
-      <c r="N11">
-        <v>33</v>
-      </c>
-      <c r="O11">
-        <v>67</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="6"/>
-        <v>20.5</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="8"/>
-        <v>27</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="9"/>
-        <v>18.833333333333332</v>
-      </c>
-      <c r="AC11">
-        <f t="shared" si="10"/>
-        <v>9</v>
-      </c>
-      <c r="AD11">
-        <f t="shared" si="5"/>
-        <v>9.8333333333333321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>79</v>
-      </c>
-      <c r="C13">
-        <v>21</v>
-      </c>
-      <c r="D13">
-        <v>20</v>
-      </c>
-      <c r="E13">
-        <v>80</v>
-      </c>
-      <c r="G13">
-        <v>94</v>
-      </c>
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13">
-        <v>18</v>
-      </c>
-      <c r="J13">
-        <v>82</v>
-      </c>
-      <c r="L13">
-        <v>81</v>
-      </c>
-      <c r="M13">
-        <v>19</v>
-      </c>
-      <c r="N13">
-        <v>35</v>
-      </c>
-      <c r="O13">
-        <v>65</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" ref="Q13:Q16" si="11">AVERAGE(C13,D13)</f>
-        <v>20.5</v>
-      </c>
-      <c r="R13">
-        <f t="shared" ref="R13:R16" si="12">AVERAGE(H13,I13)</f>
-        <v>12</v>
-      </c>
-      <c r="S13">
-        <f t="shared" ref="S13:S16" si="13">AVERAGE(M13,N13)</f>
-        <v>27</v>
-      </c>
-      <c r="T13">
-        <f t="shared" ref="T13:T16" si="14">AVERAGE(Q13:S13)</f>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="U13">
-        <f>AVERAGE(Q13:Q20)</f>
-        <v>18.75</v>
-      </c>
-      <c r="V13">
-        <f>_xlfn.STDEV.S(Q13:Q20)</f>
-        <v>1.7559422921421233</v>
-      </c>
-      <c r="W13">
-        <f>AVERAGE(R13:R20)</f>
-        <v>10.5</v>
-      </c>
-      <c r="X13">
-        <f>_xlfn.STDEV.S(R13:R20)</f>
-        <v>2.2730302828309759</v>
-      </c>
-      <c r="Y13">
-        <f>AVERAGE(S13:S20)</f>
-        <v>27.125</v>
-      </c>
-      <c r="Z13">
-        <f>_xlfn.STDEV.S(S13:S20)</f>
-        <v>1.9311050377094112</v>
-      </c>
-      <c r="AA13">
-        <f>AVERAGE(T13:T20)</f>
-        <v>18.791666666666664</v>
-      </c>
-      <c r="AB13">
-        <f>_xlfn.STDEV.S(T13:T20)</f>
-        <v>1.1252571722516165</v>
-      </c>
-      <c r="AC13">
-        <f t="shared" ref="AC13:AC16" si="15">MIN(Q13:S13)</f>
-        <v>12</v>
-      </c>
-      <c r="AD13">
-        <f t="shared" ref="AD13:AD16" si="16">(T13-AC13)</f>
-        <v>7.8333333333333321</v>
-      </c>
-      <c r="AE13">
-        <f>AVERAGE(AD13:AD20)</f>
-        <v>8.2916666666666661</v>
-      </c>
-      <c r="AF13">
-        <f>_xlfn.STDEV.S(AD13:AD20)</f>
-        <v>1.1970256348008435</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>78</v>
-      </c>
-      <c r="C14">
-        <v>22</v>
-      </c>
-      <c r="D14">
-        <v>13</v>
-      </c>
-      <c r="E14">
-        <v>87</v>
-      </c>
-      <c r="G14">
-        <v>96</v>
-      </c>
-      <c r="H14">
-        <v>4</v>
-      </c>
-      <c r="I14">
-        <v>16</v>
-      </c>
-      <c r="J14">
-        <v>84</v>
-      </c>
-      <c r="L14">
-        <v>93</v>
-      </c>
-      <c r="M14">
-        <v>7</v>
-      </c>
-      <c r="N14">
-        <v>49</v>
-      </c>
-      <c r="O14">
-        <v>51</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="11"/>
-        <v>17.5</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="12"/>
-        <v>10</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="13"/>
-        <v>28</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="14"/>
-        <v>18.5</v>
-      </c>
-      <c r="AC14">
-        <f t="shared" si="15"/>
-        <v>10</v>
-      </c>
-      <c r="AD14">
-        <f t="shared" si="16"/>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>69</v>
-      </c>
-      <c r="C15">
-        <v>31</v>
-      </c>
-      <c r="D15">
-        <v>9</v>
-      </c>
-      <c r="E15">
-        <v>91</v>
-      </c>
-      <c r="G15">
-        <v>94</v>
-      </c>
-      <c r="H15">
-        <v>6</v>
-      </c>
-      <c r="I15">
-        <v>9</v>
-      </c>
-      <c r="J15">
-        <v>91</v>
-      </c>
-      <c r="L15">
-        <v>80</v>
-      </c>
-      <c r="M15">
-        <v>20</v>
-      </c>
-      <c r="N15">
-        <v>29</v>
-      </c>
-      <c r="O15">
-        <v>71</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="11"/>
-        <v>20</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="12"/>
-        <v>7.5</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="13"/>
-        <v>24.5</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="14"/>
-        <v>17.333333333333332</v>
-      </c>
-      <c r="AC15">
-        <f t="shared" si="15"/>
-        <v>7.5</v>
-      </c>
-      <c r="AD15">
-        <f t="shared" si="16"/>
-        <v>9.8333333333333321</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>83</v>
-      </c>
-      <c r="C16">
-        <v>17</v>
-      </c>
-      <c r="D16">
-        <v>17</v>
-      </c>
-      <c r="E16">
-        <v>83</v>
-      </c>
-      <c r="G16">
-        <v>89</v>
-      </c>
-      <c r="H16">
-        <v>11</v>
-      </c>
-      <c r="I16">
-        <v>14</v>
-      </c>
-      <c r="J16">
-        <v>86</v>
-      </c>
-      <c r="L16">
-        <v>93</v>
-      </c>
-      <c r="M16">
-        <v>7</v>
-      </c>
-      <c r="N16">
-        <v>51</v>
-      </c>
-      <c r="O16">
-        <v>49</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="12"/>
-        <v>12.5</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="13"/>
-        <v>29</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="14"/>
-        <v>19.5</v>
-      </c>
-      <c r="AC16">
-        <f t="shared" si="15"/>
-        <v>12.5</v>
-      </c>
-      <c r="AD16">
-        <f t="shared" si="16"/>
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12533,6 +12954,1138 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
+  <dimension ref="A2:AF24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>72</v>
+      </c>
+      <c r="C4">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>86</v>
+      </c>
+      <c r="G4">
+        <v>96</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>86</v>
+      </c>
+      <c r="L4">
+        <v>82</v>
+      </c>
+      <c r="M4">
+        <v>18</v>
+      </c>
+      <c r="N4">
+        <v>39</v>
+      </c>
+      <c r="O4">
+        <v>61</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>21</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>9</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>28.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>19.5</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q11)</f>
+        <v>19.5625</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q11)</f>
+        <v>3.2997564845216774</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R11)</f>
+        <v>8.8125</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R11)</f>
+        <v>2.0863074009907003</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S11)</f>
+        <v>27.4375</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S11)</f>
+        <v>1.2374368670764582</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T11)</f>
+        <v>18.604166666666668</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T11)</f>
+        <v>1.4473223771821069</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <f>(T4-AC4)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD11)</f>
+        <v>9.7916666666666661</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD11)</f>
+        <v>1.6250763107845259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>79</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>88</v>
+      </c>
+      <c r="G5">
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>87</v>
+      </c>
+      <c r="L5">
+        <v>79</v>
+      </c>
+      <c r="M5">
+        <v>21</v>
+      </c>
+      <c r="N5">
+        <v>35</v>
+      </c>
+      <c r="O5">
+        <v>65</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5" si="0">AVERAGE(C5,D5)</f>
+        <v>16.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5" si="1">AVERAGE(H5,I5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5" si="2">AVERAGE(M5,N5)</f>
+        <v>28</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5" si="3">AVERAGE(Q5:S5)</f>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5" si="4">MIN(Q5:S5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD11" si="5">(T5-AC5)</f>
+        <v>7.1666666666666679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>67</v>
+      </c>
+      <c r="C6">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>88</v>
+      </c>
+      <c r="G6">
+        <v>92</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>94</v>
+      </c>
+      <c r="L6">
+        <v>70</v>
+      </c>
+      <c r="M6">
+        <v>30</v>
+      </c>
+      <c r="N6">
+        <v>23</v>
+      </c>
+      <c r="O6">
+        <v>77</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" ref="Q6:Q11" si="6">AVERAGE(C6,D6)</f>
+        <v>22.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" ref="R6:R11" si="7">AVERAGE(H6,I6)</f>
+        <v>7</v>
+      </c>
+      <c r="S6">
+        <f t="shared" ref="S6:S11" si="8">AVERAGE(M6,N6)</f>
+        <v>26.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" ref="T6:T11" si="9">AVERAGE(Q6:S6)</f>
+        <v>18.666666666666668</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" ref="AC6:AC11" si="10">MIN(Q6:S6)</f>
+        <v>7</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>11.666666666666668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>75</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>83</v>
+      </c>
+      <c r="G7">
+        <v>95</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>90</v>
+      </c>
+      <c r="L7">
+        <v>86</v>
+      </c>
+      <c r="M7">
+        <v>14</v>
+      </c>
+      <c r="N7">
+        <v>40</v>
+      </c>
+      <c r="O7">
+        <v>60</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="7"/>
+        <v>7.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="9"/>
+        <v>18.5</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="10"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>82</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>86</v>
+      </c>
+      <c r="G8">
+        <v>97</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>9</v>
+      </c>
+      <c r="J8">
+        <v>91</v>
+      </c>
+      <c r="L8">
+        <v>83</v>
+      </c>
+      <c r="M8">
+        <v>17</v>
+      </c>
+      <c r="N8">
+        <v>42</v>
+      </c>
+      <c r="O8">
+        <v>58</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="9"/>
+        <v>17.166666666666668</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>11.166666666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>89</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>81</v>
+      </c>
+      <c r="G9">
+        <v>97</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>14</v>
+      </c>
+      <c r="J9">
+        <v>86</v>
+      </c>
+      <c r="L9">
+        <v>91</v>
+      </c>
+      <c r="M9">
+        <v>9</v>
+      </c>
+      <c r="N9">
+        <v>42</v>
+      </c>
+      <c r="O9">
+        <v>58</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="7"/>
+        <v>8.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="8"/>
+        <v>25.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="9"/>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="10"/>
+        <v>8.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>7.8333333333333321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>85</v>
+      </c>
+      <c r="G10">
+        <v>93</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>17</v>
+      </c>
+      <c r="J10">
+        <v>83</v>
+      </c>
+      <c r="L10">
+        <v>81</v>
+      </c>
+      <c r="M10">
+        <v>19</v>
+      </c>
+      <c r="N10">
+        <v>36</v>
+      </c>
+      <c r="O10">
+        <v>64</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="8"/>
+        <v>27.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>9.1666666666666679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>69</v>
+      </c>
+      <c r="C11">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>90</v>
+      </c>
+      <c r="G11">
+        <v>92</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>90</v>
+      </c>
+      <c r="L11">
+        <v>79</v>
+      </c>
+      <c r="M11">
+        <v>21</v>
+      </c>
+      <c r="N11">
+        <v>33</v>
+      </c>
+      <c r="O11">
+        <v>67</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>20.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="5"/>
+        <v>9.8333333333333321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>79</v>
+      </c>
+      <c r="C13">
+        <v>21</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>94</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>82</v>
+      </c>
+      <c r="L13">
+        <v>81</v>
+      </c>
+      <c r="M13">
+        <v>19</v>
+      </c>
+      <c r="N13">
+        <v>35</v>
+      </c>
+      <c r="O13">
+        <v>65</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" ref="Q13:Q16" si="11">AVERAGE(C13,D13)</f>
+        <v>20.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" ref="R13:R16" si="12">AVERAGE(H13,I13)</f>
+        <v>12</v>
+      </c>
+      <c r="S13">
+        <f t="shared" ref="S13:S16" si="13">AVERAGE(M13,N13)</f>
+        <v>27</v>
+      </c>
+      <c r="T13">
+        <f t="shared" ref="T13:T16" si="14">AVERAGE(Q13:S13)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="U13">
+        <f>AVERAGE(Q13:Q22)</f>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="V13">
+        <f>_xlfn.STDEV.S(Q13:Q22)</f>
+        <v>1.5572411502397436</v>
+      </c>
+      <c r="W13">
+        <f>AVERAGE(R13:R22)</f>
+        <v>10.6</v>
+      </c>
+      <c r="X13">
+        <f>_xlfn.STDEV.S(R13:R22)</f>
+        <v>1.9811612756158978</v>
+      </c>
+      <c r="Y13">
+        <f>AVERAGE(S13:S22)</f>
+        <v>27.3</v>
+      </c>
+      <c r="Z13">
+        <f>_xlfn.STDEV.S(S13:S22)</f>
+        <v>1.7175564037317668</v>
+      </c>
+      <c r="AA13">
+        <f>AVERAGE(T13:T22)</f>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="AB13">
+        <f>_xlfn.STDEV.S(T13:T22)</f>
+        <v>0.97894501037256099</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" ref="AC13:AC16" si="15">MIN(Q13:S13)</f>
+        <v>12</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" ref="AD13:AD16" si="16">(T13-AC13)</f>
+        <v>7.8333333333333321</v>
+      </c>
+      <c r="AE13">
+        <f>AVERAGE(AD13:AD22)</f>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="AF13">
+        <f>_xlfn.STDEV.S(AD13:AD22)</f>
+        <v>1.0448285345771593</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>78</v>
+      </c>
+      <c r="C14">
+        <v>22</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>87</v>
+      </c>
+      <c r="G14">
+        <v>96</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>16</v>
+      </c>
+      <c r="J14">
+        <v>84</v>
+      </c>
+      <c r="L14">
+        <v>93</v>
+      </c>
+      <c r="M14">
+        <v>7</v>
+      </c>
+      <c r="N14">
+        <v>49</v>
+      </c>
+      <c r="O14">
+        <v>51</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="11"/>
+        <v>17.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="13"/>
+        <v>28</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="14"/>
+        <v>18.5</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="16"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>69</v>
+      </c>
+      <c r="C15">
+        <v>31</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>91</v>
+      </c>
+      <c r="G15">
+        <v>94</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>9</v>
+      </c>
+      <c r="J15">
+        <v>91</v>
+      </c>
+      <c r="L15">
+        <v>80</v>
+      </c>
+      <c r="M15">
+        <v>20</v>
+      </c>
+      <c r="N15">
+        <v>29</v>
+      </c>
+      <c r="O15">
+        <v>71</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="12"/>
+        <v>7.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="13"/>
+        <v>24.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="14"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="15"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="16"/>
+        <v>9.8333333333333321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>17</v>
+      </c>
+      <c r="E16">
+        <v>83</v>
+      </c>
+      <c r="G16">
+        <v>89</v>
+      </c>
+      <c r="H16">
+        <v>11</v>
+      </c>
+      <c r="I16">
+        <v>14</v>
+      </c>
+      <c r="J16">
+        <v>86</v>
+      </c>
+      <c r="L16">
+        <v>93</v>
+      </c>
+      <c r="M16">
+        <v>7</v>
+      </c>
+      <c r="N16">
+        <v>51</v>
+      </c>
+      <c r="O16">
+        <v>49</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="12"/>
+        <v>12.5</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="14"/>
+        <v>19.5</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="15"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="16"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>88</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>24</v>
+      </c>
+      <c r="E22">
+        <v>76</v>
+      </c>
+      <c r="G22">
+        <v>97</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>19</v>
+      </c>
+      <c r="J22">
+        <v>81</v>
+      </c>
+      <c r="L22">
+        <v>80</v>
+      </c>
+      <c r="M22">
+        <v>20</v>
+      </c>
+      <c r="N22">
+        <v>36</v>
+      </c>
+      <c r="O22">
+        <v>64</v>
+      </c>
+      <c r="Q22">
+        <f>AVERAGE(C22,D22)</f>
+        <v>18</v>
+      </c>
+      <c r="R22">
+        <f>AVERAGE(H22,I22)</f>
+        <v>11</v>
+      </c>
+      <c r="S22">
+        <f>AVERAGE(M22,N22)</f>
+        <v>28</v>
+      </c>
+      <c r="T22">
+        <f>AVERAGE(Q22:S22)</f>
+        <v>19</v>
+      </c>
+      <c r="U22">
+        <f>AVERAGE(Q22:Q31)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="V22">
+        <f>_xlfn.STDEV.S(Q22:Q31)</f>
+        <v>3.0138568866708604</v>
+      </c>
+      <c r="W22">
+        <f>AVERAGE(R22:R31)</f>
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="X22">
+        <f>_xlfn.STDEV.S(R22:R31)</f>
+        <v>1.5275252316519499</v>
+      </c>
+      <c r="Y22">
+        <f>AVERAGE(S22:S31)</f>
+        <v>30.666666666666668</v>
+      </c>
+      <c r="Z22">
+        <f>_xlfn.STDEV.S(S22:S31)</f>
+        <v>3.0550504633038935</v>
+      </c>
+      <c r="AA22">
+        <f>AVERAGE(T22:T31)</f>
+        <v>20.388888888888889</v>
+      </c>
+      <c r="AB22">
+        <f>_xlfn.STDEV.S(T22:T31)</f>
+        <v>1.9883922409081429</v>
+      </c>
+      <c r="AC22">
+        <f>MIN(Q22:S22)</f>
+        <v>11</v>
+      </c>
+      <c r="AD22">
+        <f>(T22-AC22)</f>
+        <v>8</v>
+      </c>
+      <c r="AE22">
+        <f>AVERAGE(AD22:AD31)</f>
+        <v>10.722222222222223</v>
+      </c>
+      <c r="AF22">
+        <f>_xlfn.STDEV.S(AD22:AD31)</f>
+        <v>2.4286103327104773</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>74</v>
+      </c>
+      <c r="C23">
+        <v>26</v>
+      </c>
+      <c r="D23">
+        <v>15</v>
+      </c>
+      <c r="E23">
+        <v>85</v>
+      </c>
+      <c r="G23">
+        <v>96</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>12</v>
+      </c>
+      <c r="J23">
+        <v>88</v>
+      </c>
+      <c r="L23">
+        <v>84</v>
+      </c>
+      <c r="M23">
+        <v>16</v>
+      </c>
+      <c r="N23">
+        <v>44</v>
+      </c>
+      <c r="O23">
+        <v>56</v>
+      </c>
+      <c r="Q23">
+        <f>AVERAGE(C23,D23)</f>
+        <v>20.5</v>
+      </c>
+      <c r="R23">
+        <f>AVERAGE(H23,I23)</f>
+        <v>8</v>
+      </c>
+      <c r="S23">
+        <f>AVERAGE(M23,N23)</f>
+        <v>30</v>
+      </c>
+      <c r="T23">
+        <f>AVERAGE(Q23:S23)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AC23">
+        <f>MIN(Q23:S23)</f>
+        <v>8</v>
+      </c>
+      <c r="AD23">
+        <f>(T23-AC23)</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>69</v>
+      </c>
+      <c r="C24">
+        <v>31</v>
+      </c>
+      <c r="D24">
+        <v>17</v>
+      </c>
+      <c r="E24">
+        <v>83</v>
+      </c>
+      <c r="G24">
+        <v>93</v>
+      </c>
+      <c r="H24">
+        <v>7</v>
+      </c>
+      <c r="I24">
+        <v>13</v>
+      </c>
+      <c r="J24">
+        <v>87</v>
+      </c>
+      <c r="L24">
+        <v>71</v>
+      </c>
+      <c r="M24">
+        <v>29</v>
+      </c>
+      <c r="N24">
+        <v>39</v>
+      </c>
+      <c r="O24">
+        <v>61</v>
+      </c>
+      <c r="Q24">
+        <f>AVERAGE(C24,D24)</f>
+        <v>24</v>
+      </c>
+      <c r="R24">
+        <f>AVERAGE(H24,I24)</f>
+        <v>10</v>
+      </c>
+      <c r="S24">
+        <f>AVERAGE(M24,N24)</f>
+        <v>34</v>
+      </c>
+      <c r="T24">
+        <f>AVERAGE(Q24:S24)</f>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC24">
+        <f>MIN(Q24:S24)</f>
+        <v>10</v>
+      </c>
+      <c r="AD24">
+        <f>(T24-AC24)</f>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12695,7 +14248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13122,7 +14675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13609,493 +15162,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>82</v>
-      </c>
-      <c r="C4">
-        <v>18</v>
-      </c>
-      <c r="D4">
-        <v>12</v>
-      </c>
-      <c r="E4">
-        <v>88</v>
-      </c>
-      <c r="G4">
-        <v>99</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>86</v>
-      </c>
-      <c r="L4">
-        <v>80</v>
-      </c>
-      <c r="M4">
-        <v>20</v>
-      </c>
-      <c r="N4">
-        <v>33</v>
-      </c>
-      <c r="O4">
-        <v>67</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>15</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>7.5</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>26.5</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>16.333333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q9)</f>
-        <v>17.833333333333332</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q9)</f>
-        <v>3.125166662222457</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R9)</f>
-        <v>8.5833333333333339</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R9)</f>
-        <v>1.2416387021459434</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S9)</f>
-        <v>28.583333333333332</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S9)</f>
-        <v>3.6799003609699281</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T9)</f>
-        <v>18.333333333333332</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T9)</f>
-        <v>1.7763883459298975</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>7.5</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>8.8333333333333321</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD9)</f>
-        <v>9.75</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD9)</f>
-        <v>1.0632758605157719</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>70</v>
-      </c>
-      <c r="C5">
-        <v>30</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>83</v>
-      </c>
-      <c r="G5">
-        <v>92</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>88</v>
-      </c>
-      <c r="L5">
-        <v>85</v>
-      </c>
-      <c r="M5">
-        <v>15</v>
-      </c>
-      <c r="N5">
-        <v>39</v>
-      </c>
-      <c r="O5">
-        <v>61</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
-        <v>23.5</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
-        <v>10</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
-        <v>27</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
-        <v>20.166666666666668</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
-        <v>10</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD9" si="5">T5-AC5</f>
-        <v>10.166666666666668</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>82</v>
-      </c>
-      <c r="C6">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>87</v>
-      </c>
-      <c r="G6">
-        <v>96</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>89</v>
-      </c>
-      <c r="L6">
-        <v>75</v>
-      </c>
-      <c r="M6">
-        <v>25</v>
-      </c>
-      <c r="N6">
-        <v>40</v>
-      </c>
-      <c r="O6">
-        <v>60</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>15.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>32.5</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>18.5</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>7.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>82</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>80</v>
-      </c>
-      <c r="G7">
-        <v>93</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>89</v>
-      </c>
-      <c r="L7">
-        <v>76</v>
-      </c>
-      <c r="M7">
-        <v>24</v>
-      </c>
-      <c r="N7">
-        <v>39</v>
-      </c>
-      <c r="O7">
-        <v>61</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>31.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>10.833333333333332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>79</v>
-      </c>
-      <c r="C8">
-        <v>21</v>
-      </c>
-      <c r="D8">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>86</v>
-      </c>
-      <c r="G8">
-        <v>95</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>90</v>
-      </c>
-      <c r="L8">
-        <v>86</v>
-      </c>
-      <c r="M8">
-        <v>14</v>
-      </c>
-      <c r="N8">
-        <v>32</v>
-      </c>
-      <c r="O8">
-        <v>68</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>17.5</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>7.5</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>78</v>
-      </c>
-      <c r="C9">
-        <v>22</v>
-      </c>
-      <c r="D9">
-        <v>11</v>
-      </c>
-      <c r="E9">
-        <v>89</v>
-      </c>
-      <c r="G9">
-        <v>93</v>
-      </c>
-      <c r="H9">
-        <v>7</v>
-      </c>
-      <c r="I9">
-        <v>13</v>
-      </c>
-      <c r="J9">
-        <v>87</v>
-      </c>
-      <c r="L9">
-        <v>76</v>
-      </c>
-      <c r="M9">
-        <v>24</v>
-      </c>
-      <c r="N9">
-        <v>38</v>
-      </c>
-      <c r="O9">
-        <v>62</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>31</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>19.166666666666668</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>9.1666666666666679</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DataAnalysis/LF/0.05/Results.xlsx
+++ b/DataAnalysis/LF/0.05/Results.xlsx
@@ -8,29 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LF\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC78586D-DEDB-4108-B364-90DFBBFF50A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DBCB2D-2B87-4187-95C7-BCAD97F1E109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId4"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId8"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId9"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId10"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId11"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
+    <sheet name="DIFF_ONLYMIN" sheetId="21" r:id="rId2"/>
+    <sheet name="PARBS_STDAUG" sheetId="20" r:id="rId3"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId4"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId5"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId6"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId7"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId8"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId9"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId10"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId11"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId12"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId13"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId14"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId16"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId17"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId18"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="73">
   <si>
     <t>Dati originali</t>
   </si>
@@ -589,13 +590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -630,12 +631,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>4</v>
       </c>
@@ -670,7 +671,7 @@
         <v>3.8345408726083114</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
@@ -707,18 +708,51 @@
       <c r="P4">
         <v>2.523959264800121</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R4">
+        <v>17.75</v>
+      </c>
+      <c r="S4">
+        <v>5.3033008588991066</v>
+      </c>
+      <c r="T4">
+        <v>10.75</v>
+      </c>
+      <c r="U4">
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="V4">
+        <v>34</v>
+      </c>
+      <c r="W4">
+        <v>2.1213203435596424</v>
+      </c>
+      <c r="X4">
+        <v>20.833333333333332</v>
+      </c>
+      <c r="Y4">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="Z4">
+        <v>10.083333333333332</v>
+      </c>
+      <c r="AA4">
+        <v>1.7677669529663689</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
         <v>43</v>
       </c>
@@ -756,12 +790,12 @@
         <v>2.0744254001387374</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
         <v>43</v>
       </c>
@@ -799,7 +833,7 @@
         <v>1.8627687476998984</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>48</v>
       </c>
@@ -834,7 +868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>71</v>
       </c>
@@ -863,516 +897,589 @@
         <v>0.41943524640393165</v>
       </c>
       <c r="O11">
-        <v>7.3888888888888893</v>
+        <v>7.3888888888888902</v>
       </c>
       <c r="P11">
         <v>2.7504208432192381</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13">
+        <v>19.5</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>10.75</v>
+      </c>
+      <c r="J13">
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="K13">
+        <v>29</v>
+      </c>
+      <c r="L13">
+        <v>5.6568542494923806</v>
+      </c>
+      <c r="M13">
+        <v>19.75</v>
+      </c>
+      <c r="N13">
+        <v>2.7105759945484338</v>
+      </c>
+      <c r="O13">
+        <v>9</v>
+      </c>
+      <c r="P13">
+        <v>0.2357022603955175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
         <v>4</v>
       </c>
-      <c r="G13">
+      <c r="G16">
         <v>22.15</v>
       </c>
-      <c r="H13">
+      <c r="H16">
         <v>1.8566696588844833</v>
       </c>
-      <c r="I13">
+      <c r="I16">
         <v>15</v>
       </c>
-      <c r="J13">
+      <c r="J16">
         <v>1.986062547968831</v>
       </c>
-      <c r="K13">
+      <c r="K16">
         <v>30.5</v>
       </c>
-      <c r="L13">
+      <c r="L16">
         <v>2.8674417556808756</v>
       </c>
-      <c r="M13">
+      <c r="M16">
         <v>22.549999999999997</v>
       </c>
-      <c r="N13">
+      <c r="N16">
         <v>1.0454191669220056</v>
       </c>
-      <c r="O13">
+      <c r="O16">
         <v>7.5500000000000016</v>
       </c>
-      <c r="P13">
+      <c r="P16">
         <v>2.3014354082336492</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F17" t="s">
         <v>21</v>
       </c>
-      <c r="G14">
+      <c r="G17">
         <v>19</v>
       </c>
-      <c r="H14">
+      <c r="H17">
         <v>2.2360679774997898</v>
       </c>
-      <c r="I14">
+      <c r="I17">
         <v>11.1875</v>
       </c>
-      <c r="J14">
+      <c r="J17">
         <v>2.2350695099449847</v>
       </c>
-      <c r="K14">
+      <c r="K17">
         <v>26.6875</v>
       </c>
-      <c r="L14">
+      <c r="L17">
         <v>3.0930509672028177</v>
       </c>
-      <c r="M14">
+      <c r="M17">
         <v>18.958333333333332</v>
       </c>
-      <c r="N14">
+      <c r="N17">
         <v>0.7955730688858863</v>
       </c>
-      <c r="O14">
+      <c r="O17">
         <v>7.7708333333333339</v>
       </c>
-      <c r="P14">
+      <c r="P17">
         <v>2.3936713848004882</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>4</v>
       </c>
-      <c r="G17">
+      <c r="G20">
         <v>23.214285714285715</v>
       </c>
-      <c r="H17">
+      <c r="H20">
         <v>2.6435005651777832</v>
       </c>
-      <c r="I17">
+      <c r="I20">
         <v>11.071428571428571</v>
       </c>
-      <c r="J17">
+      <c r="J20">
         <v>1.336306209562119</v>
       </c>
-      <c r="K17">
+      <c r="K20">
         <v>35.642857142857146</v>
       </c>
-      <c r="L17">
+      <c r="L20">
         <v>4.5434411125112195</v>
       </c>
-      <c r="M17">
+      <c r="M20">
         <v>23.309523809523807</v>
       </c>
-      <c r="N17">
+      <c r="N20">
         <v>1.5257923607235448</v>
       </c>
-      <c r="O17">
+      <c r="O20">
         <v>12.238095238095239</v>
       </c>
-      <c r="P17">
+      <c r="P20">
         <v>2.088010622527662</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
         <v>64</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F21" t="s">
         <v>21</v>
       </c>
-      <c r="G18">
+      <c r="G21">
         <v>17.833333333333332</v>
       </c>
-      <c r="H18">
+      <c r="H21">
         <v>3.125166662222457</v>
       </c>
-      <c r="I18">
+      <c r="I21">
         <v>8.5833333333333339</v>
       </c>
-      <c r="J18">
+      <c r="J21">
         <v>1.2416387021459434</v>
       </c>
-      <c r="K18">
+      <c r="K21">
         <v>28.583333333333332</v>
       </c>
-      <c r="L18">
+      <c r="L21">
         <v>3.6799003609699281</v>
       </c>
-      <c r="M18">
+      <c r="M21">
         <v>18.333333333333332</v>
       </c>
-      <c r="N18">
+      <c r="N21">
         <v>1.7763883459298975</v>
       </c>
-      <c r="O18">
+      <c r="O21">
         <v>9.75</v>
       </c>
-      <c r="P18">
+      <c r="P21">
         <v>1.0632758605157719</v>
       </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
+      <c r="Q21" t="s">
+        <v>71</v>
+      </c>
+      <c r="R21">
+        <v>20</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>10</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>29.5</v>
+      </c>
+      <c r="W21">
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="X21">
+        <v>19.833333333333336</v>
+      </c>
+      <c r="Y21">
+        <v>0.47140452079103251</v>
+      </c>
+      <c r="Z21">
+        <v>9.8333333333333339</v>
+      </c>
+      <c r="AA21">
+        <v>0.47140452079103251</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
         <v>64</v>
       </c>
-      <c r="G20">
+      <c r="G23">
         <v>18.75</v>
       </c>
-      <c r="H20">
+      <c r="H23">
         <v>1.7559422921421233</v>
       </c>
-      <c r="I20">
+      <c r="I23">
         <v>10.5</v>
       </c>
-      <c r="J20">
+      <c r="J23">
         <v>2.2730302828309759</v>
       </c>
-      <c r="K20">
+      <c r="K23">
         <v>27.125</v>
       </c>
-      <c r="L20">
+      <c r="L23">
         <v>1.9311050377094112</v>
       </c>
-      <c r="M20">
+      <c r="M23">
         <v>18.791666666666664</v>
       </c>
-      <c r="N20">
+      <c r="N23">
         <v>1.1252571722516165</v>
       </c>
-      <c r="O20">
+      <c r="O23">
         <v>8.2916666666666661</v>
       </c>
-      <c r="P20">
+      <c r="P23">
         <v>1.1970256348008435</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="F21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21">
-        <v>20.833333333333332</v>
-      </c>
-      <c r="H21">
-        <v>3.0138568866708604</v>
-      </c>
-      <c r="I21">
-        <v>9.6666666666666661</v>
-      </c>
-      <c r="J21">
-        <v>1.5275252316519499</v>
-      </c>
-      <c r="K21">
-        <v>30.666666666666668</v>
-      </c>
-      <c r="L21">
-        <v>3.0550504633038935</v>
-      </c>
-      <c r="M21">
-        <v>20.388888888888889</v>
-      </c>
-      <c r="N21">
-        <v>1.9883922409081429</v>
-      </c>
-      <c r="O21">
-        <v>10.722222222222223</v>
-      </c>
-      <c r="P21">
-        <v>2.4286103327104773</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E23" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23">
-        <v>17.375</v>
-      </c>
-      <c r="H23">
-        <v>2.75</v>
-      </c>
-      <c r="I23">
-        <v>10.375</v>
-      </c>
-      <c r="J23">
-        <v>3.4490336810958131</v>
-      </c>
-      <c r="K23">
-        <v>28.625</v>
-      </c>
-      <c r="L23">
-        <v>3.0103986446980739</v>
-      </c>
-      <c r="M23">
-        <v>18.791666666666668</v>
-      </c>
-      <c r="N23">
-        <v>2.5725581734055121</v>
-      </c>
-      <c r="O23">
-        <v>8.4166666666666679</v>
-      </c>
-      <c r="P23">
-        <v>1.6583123951776941</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="F24" t="s">
         <v>71</v>
       </c>
       <c r="G24">
+        <v>20.833333333333332</v>
+      </c>
+      <c r="H24">
+        <v>3.0138568866708604</v>
+      </c>
+      <c r="I24">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="J24">
+        <v>1.5275252316519499</v>
+      </c>
+      <c r="K24">
+        <v>30.666666666666668</v>
+      </c>
+      <c r="L24">
+        <v>3.0550504633038935</v>
+      </c>
+      <c r="M24">
+        <v>20.388888888888889</v>
+      </c>
+      <c r="N24">
+        <v>1.9883922409081429</v>
+      </c>
+      <c r="O24">
+        <v>10.7222222222222</v>
+      </c>
+      <c r="P24">
+        <v>2.4286103327104773</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26">
+        <v>17.375</v>
+      </c>
+      <c r="H26">
+        <v>2.75</v>
+      </c>
+      <c r="I26">
+        <v>10.375</v>
+      </c>
+      <c r="J26">
+        <v>3.4490336810958131</v>
+      </c>
+      <c r="K26">
+        <v>28.625</v>
+      </c>
+      <c r="L26">
+        <v>3.0103986446980739</v>
+      </c>
+      <c r="M26">
+        <v>18.791666666666668</v>
+      </c>
+      <c r="N26">
+        <v>2.5725581734055121</v>
+      </c>
+      <c r="O26">
+        <v>8.4166666666666679</v>
+      </c>
+      <c r="P26">
+        <v>1.6583123951776941</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27">
         <v>17.5</v>
       </c>
-      <c r="H24">
+      <c r="H27">
         <v>2.598076211353316</v>
       </c>
-      <c r="I24">
+      <c r="I27">
         <v>10</v>
       </c>
-      <c r="J24">
+      <c r="J27">
         <v>2.179449471770337</v>
       </c>
-      <c r="K24">
+      <c r="K27">
         <v>30.333333333333332</v>
       </c>
-      <c r="L24">
+      <c r="L27">
         <v>2.8431203515386634</v>
       </c>
-      <c r="M24">
+      <c r="M27">
         <v>19.277777777777775</v>
       </c>
-      <c r="N24">
+      <c r="N27">
         <v>1.8282758524338136</v>
       </c>
-      <c r="O24">
+      <c r="O27">
         <v>9.2777777777777768</v>
       </c>
-      <c r="P24">
+      <c r="P27">
         <v>2.219442706159791</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>4</v>
       </c>
-      <c r="G27">
+      <c r="G30">
         <v>19.583333333333332</v>
       </c>
-      <c r="H27">
+      <c r="H30">
         <v>2.3540744819709287</v>
       </c>
-      <c r="I27">
+      <c r="I30">
         <v>13.916666666666666</v>
       </c>
-      <c r="J27">
+      <c r="J30">
         <v>2.5380438661825075</v>
       </c>
-      <c r="K27">
+      <c r="K30">
         <v>23</v>
       </c>
-      <c r="L27">
+      <c r="L30">
         <v>5.196152422706632</v>
       </c>
-      <c r="M27">
+      <c r="M30">
         <v>18.833333333333332</v>
       </c>
-      <c r="N27">
+      <c r="N30">
         <v>1.8737959096740264</v>
       </c>
-      <c r="O27">
+      <c r="O30">
         <v>4.916666666666667</v>
       </c>
-      <c r="P27">
+      <c r="P30">
         <v>2.1337239225770932</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
         <v>64</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F31" t="s">
         <v>21</v>
       </c>
-      <c r="G28">
+      <c r="G31">
         <v>21.1</v>
       </c>
-      <c r="H28">
+      <c r="H31">
         <v>3.8307962618755846</v>
       </c>
-      <c r="I28">
+      <c r="I31">
         <v>11.9</v>
       </c>
-      <c r="J28">
+      <c r="J31">
         <v>3.7316216314090598</v>
       </c>
-      <c r="K28">
+      <c r="K31">
         <v>24.4</v>
       </c>
-      <c r="L28">
+      <c r="L31">
         <v>3.2093613071762355</v>
       </c>
-      <c r="M28">
+      <c r="M31">
         <v>19.133333333333333</v>
       </c>
-      <c r="N28">
+      <c r="N31">
         <v>1.8234582528810472</v>
       </c>
-      <c r="O28">
+      <c r="O31">
         <v>7.2333333333333343</v>
       </c>
-      <c r="P28">
+      <c r="P31">
         <v>3.1898275815473136</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
         <v>64</v>
       </c>
-      <c r="F30" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30">
-        <v>14.833333333333334</v>
-      </c>
-      <c r="H30">
-        <v>1.2583057392117918</v>
-      </c>
-      <c r="I30">
-        <v>10.166666666666666</v>
-      </c>
-      <c r="J30">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="K30">
-        <v>21.5</v>
-      </c>
-      <c r="L30">
-        <v>3.5</v>
-      </c>
-      <c r="M30">
-        <v>15.5</v>
-      </c>
-      <c r="N30">
-        <v>1.0408329997330656</v>
-      </c>
-      <c r="O30">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="P30">
-        <v>0.8660254037844386</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32">
-        <v>17.5</v>
-      </c>
-      <c r="H32">
-        <v>4.2720018726587652</v>
-      </c>
-      <c r="I32">
-        <v>12.333333333333334</v>
-      </c>
-      <c r="J32">
-        <v>1.2583057392117918</v>
-      </c>
-      <c r="K32">
-        <v>25.666666666666668</v>
-      </c>
-      <c r="L32">
-        <v>5.7518113089124689</v>
-      </c>
-      <c r="M32">
-        <v>18.5</v>
-      </c>
-      <c r="N32">
-        <v>3.3706247360261101</v>
-      </c>
-      <c r="O32">
-        <v>6.166666666666667</v>
-      </c>
-      <c r="P32">
-        <v>2.3154073315749666</v>
-      </c>
-    </row>
-    <row r="33" spans="6:16" x14ac:dyDescent="0.3">
       <c r="F33" t="s">
         <v>71</v>
       </c>
       <c r="G33">
+        <v>14.833333333333334</v>
+      </c>
+      <c r="H33">
+        <v>1.2583057392117918</v>
+      </c>
+      <c r="I33">
+        <v>10.166666666666666</v>
+      </c>
+      <c r="J33">
+        <v>0.28867513459481292</v>
+      </c>
+      <c r="K33">
+        <v>21.5</v>
+      </c>
+      <c r="L33">
+        <v>3.5</v>
+      </c>
+      <c r="M33">
+        <v>15.5</v>
+      </c>
+      <c r="N33">
+        <v>1.0408329997330656</v>
+      </c>
+      <c r="O33">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="P33">
+        <v>0.8660254037844386</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35">
+        <v>17.5</v>
+      </c>
+      <c r="H35">
+        <v>4.2720018726587652</v>
+      </c>
+      <c r="I35">
+        <v>12.333333333333334</v>
+      </c>
+      <c r="J35">
+        <v>1.2583057392117918</v>
+      </c>
+      <c r="K35">
+        <v>25.666666666666668</v>
+      </c>
+      <c r="L35">
+        <v>5.7518113089124689</v>
+      </c>
+      <c r="M35">
+        <v>18.5</v>
+      </c>
+      <c r="N35">
+        <v>3.3706247360261101</v>
+      </c>
+      <c r="O35">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="P35">
+        <v>2.3154073315749666</v>
+      </c>
+    </row>
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36">
         <v>20</v>
       </c>
-      <c r="H33">
+      <c r="H36">
         <v>0.70710678118654757</v>
       </c>
-      <c r="I33">
+      <c r="I36">
         <v>8.75</v>
       </c>
-      <c r="J33">
+      <c r="J36">
         <v>0.35355339059327379</v>
       </c>
-      <c r="K33">
+      <c r="K36">
         <v>23</v>
       </c>
-      <c r="L33">
+      <c r="L36">
         <v>4.2426406871192848</v>
       </c>
-      <c r="M33">
+      <c r="M36">
         <v>17.25</v>
       </c>
-      <c r="N33">
+      <c r="N36">
         <v>1.2963624321753389</v>
       </c>
-      <c r="O33">
+      <c r="O36">
         <v>8.5</v>
       </c>
-      <c r="P33">
+      <c r="P36">
         <v>0.94280904158206502</v>
       </c>
     </row>
@@ -1383,7 +1490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1453,154 +1560,154 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G4">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L4">
+        <v>87</v>
+      </c>
+      <c r="M4">
+        <v>13</v>
+      </c>
+      <c r="N4">
+        <v>20</v>
+      </c>
+      <c r="O4">
         <v>80</v>
-      </c>
-      <c r="M4">
-        <v>20</v>
-      </c>
-      <c r="N4">
-        <v>33</v>
-      </c>
-      <c r="O4">
-        <v>67</v>
       </c>
       <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>15</v>
+        <v>23.5</v>
       </c>
       <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>26.5</v>
+        <v>16.5</v>
       </c>
       <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>16.333333333333332</v>
+        <v>17.833333333333332</v>
       </c>
       <c r="U4">
         <f>AVERAGE(Q4:Q9)</f>
-        <v>17.833333333333332</v>
+        <v>19.583333333333332</v>
       </c>
       <c r="V4">
         <f>_xlfn.STDEV.S(Q4:Q9)</f>
-        <v>3.125166662222457</v>
+        <v>2.3540744819709287</v>
       </c>
       <c r="W4">
         <f>AVERAGE(R4:R9)</f>
-        <v>8.5833333333333339</v>
+        <v>13.916666666666666</v>
       </c>
       <c r="X4">
         <f>_xlfn.STDEV.S(R4:R9)</f>
-        <v>1.2416387021459434</v>
+        <v>2.5380438661825075</v>
       </c>
       <c r="Y4">
-        <f>AVERAGE(S4:S9)</f>
-        <v>28.583333333333332</v>
+        <f>AVERAGE(S4:S10)</f>
+        <v>23</v>
       </c>
       <c r="Z4">
         <f>_xlfn.STDEV.S(S4:S9)</f>
-        <v>3.6799003609699281</v>
+        <v>5.196152422706632</v>
       </c>
       <c r="AA4">
         <f>AVERAGE(T4:T9)</f>
-        <v>18.333333333333332</v>
+        <v>18.833333333333332</v>
       </c>
       <c r="AB4">
         <f>_xlfn.STDEV.S(T4:T9)</f>
-        <v>1.7763883459298975</v>
+        <v>1.8737959096740264</v>
       </c>
       <c r="AC4">
         <f>MIN(Q4:S4)</f>
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD4">
         <f>T4-AC4</f>
-        <v>8.8333333333333321</v>
+        <v>4.3333333333333321</v>
       </c>
       <c r="AE4">
         <f>AVERAGE(AD4:AD9)</f>
-        <v>9.75</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="AF4">
         <f>_xlfn.STDEV.S(AD4:AD9)</f>
-        <v>1.0632758605157719</v>
+        <v>2.1337239225770932</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L5">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N5">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="Q5">
         <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
-        <v>23.5</v>
+        <v>21</v>
       </c>
       <c r="R5">
         <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S5">
         <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
-        <v>27</v>
+        <v>22.5</v>
       </c>
       <c r="T5">
         <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
@@ -1608,11 +1715,11 @@
       </c>
       <c r="AC5">
         <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AD5">
         <f t="shared" ref="AD5:AD9" si="5">T5-AC5</f>
-        <v>10.166666666666668</v>
+        <v>3.1666666666666679</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
@@ -1620,208 +1727,208 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C6">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G6">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="S6">
         <f t="shared" si="2"/>
-        <v>32.5</v>
+        <v>25</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC6">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="AD6">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G7">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J7">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L7">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N7">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="O7">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="S7">
         <f t="shared" si="2"/>
-        <v>31.5</v>
+        <v>27</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>19.833333333333332</v>
+        <v>20</v>
       </c>
       <c r="AC7">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AD7">
         <f t="shared" si="5"/>
-        <v>10.833333333333332</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B8">
+        <v>82</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>82</v>
+      </c>
+      <c r="G8">
+        <v>81</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>88</v>
+      </c>
+      <c r="L8">
         <v>79</v>
       </c>
-      <c r="C8">
+      <c r="M8">
         <v>21</v>
       </c>
-      <c r="D8">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>86</v>
-      </c>
-      <c r="G8">
-        <v>95</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>90</v>
-      </c>
-      <c r="L8">
-        <v>86</v>
-      </c>
-      <c r="M8">
-        <v>14</v>
-      </c>
       <c r="N8">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O8">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="S8">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>29.5</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AC8">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD8">
         <f t="shared" si="5"/>
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I9">
         <v>13</v>
@@ -1830,40 +1937,40 @@
         <v>87</v>
       </c>
       <c r="L9">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="M9">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="N9">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="O9">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="Q9">
         <f t="shared" si="0"/>
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="R9">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="S9">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>17.5</v>
       </c>
       <c r="T9">
         <f t="shared" si="3"/>
-        <v>19.166666666666668</v>
+        <v>16</v>
       </c>
       <c r="AC9">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AD9">
         <f t="shared" si="5"/>
-        <v>9.1666666666666679</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -1872,6 +1979,714 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
+  <dimension ref="A2:AF13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>88</v>
+      </c>
+      <c r="G4">
+        <v>99</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>86</v>
+      </c>
+      <c r="L4">
+        <v>80</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>33</v>
+      </c>
+      <c r="O4">
+        <v>67</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>7.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>26.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q9)</f>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q9)</f>
+        <v>3.125166662222457</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R9)</f>
+        <v>8.5833333333333339</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R9)</f>
+        <v>1.2416387021459434</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S9)</f>
+        <v>28.583333333333332</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S9)</f>
+        <v>3.6799003609699281</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T9)</f>
+        <v>18.333333333333332</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T9)</f>
+        <v>1.7763883459298975</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>7.5</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD9)</f>
+        <v>9.75</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD9)</f>
+        <v>1.0632758605157719</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>70</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="G5">
+        <v>92</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>88</v>
+      </c>
+      <c r="L5">
+        <v>85</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>39</v>
+      </c>
+      <c r="O5">
+        <v>61</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
+        <v>23.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
+        <v>10</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
+        <v>27</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD9" si="5">T5-AC5</f>
+        <v>10.166666666666668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>82</v>
+      </c>
+      <c r="C6">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>87</v>
+      </c>
+      <c r="G6">
+        <v>96</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>89</v>
+      </c>
+      <c r="L6">
+        <v>75</v>
+      </c>
+      <c r="M6">
+        <v>25</v>
+      </c>
+      <c r="N6">
+        <v>40</v>
+      </c>
+      <c r="O6">
+        <v>60</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>32.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>18.5</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>82</v>
+      </c>
+      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>80</v>
+      </c>
+      <c r="G7">
+        <v>93</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>89</v>
+      </c>
+      <c r="L7">
+        <v>76</v>
+      </c>
+      <c r="M7">
+        <v>24</v>
+      </c>
+      <c r="N7">
+        <v>39</v>
+      </c>
+      <c r="O7">
+        <v>61</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>31.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>10.833333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>79</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>86</v>
+      </c>
+      <c r="G8">
+        <v>95</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>90</v>
+      </c>
+      <c r="L8">
+        <v>86</v>
+      </c>
+      <c r="M8">
+        <v>14</v>
+      </c>
+      <c r="N8">
+        <v>32</v>
+      </c>
+      <c r="O8">
+        <v>68</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>78</v>
+      </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9">
+        <v>89</v>
+      </c>
+      <c r="G9">
+        <v>93</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>13</v>
+      </c>
+      <c r="J9">
+        <v>87</v>
+      </c>
+      <c r="L9">
+        <v>76</v>
+      </c>
+      <c r="M9">
+        <v>24</v>
+      </c>
+      <c r="N9">
+        <v>38</v>
+      </c>
+      <c r="O9">
+        <v>62</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>9.1666666666666679</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="Q10" t="e">
+        <f t="shared" ref="Q10:Q13" si="6">AVERAGE(C10,D10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" t="e">
+        <f t="shared" ref="R10:R13" si="7">AVERAGE(H10,I10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S10" t="e">
+        <f t="shared" ref="S10:S13" si="8">AVERAGE(M10,N10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T10" t="e">
+        <f t="shared" ref="T10:T13" si="9">AVERAGE(Q10:S10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC10" t="e">
+        <f t="shared" ref="AC10:AC13" si="10">MIN(Q10:S10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD10" t="e">
+        <f t="shared" ref="AD10:AD13" si="11">T10-AC10</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R11" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S11" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T11" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC11" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD11" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>77</v>
+      </c>
+      <c r="G12">
+        <v>93</v>
+      </c>
+      <c r="H12">
+        <v>7</v>
+      </c>
+      <c r="I12">
+        <v>13</v>
+      </c>
+      <c r="J12">
+        <v>87</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>51</v>
+      </c>
+      <c r="O12">
+        <v>49</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>30.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U12">
+        <f>AVERAGE(Q12:Q17)</f>
+        <v>20</v>
+      </c>
+      <c r="V12">
+        <f>_xlfn.STDEV.S(Q12:Q17)</f>
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(R12:R17)</f>
+        <v>10</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(R12:R17)</f>
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(S12:S17)</f>
+        <v>29.5</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(S12:S17)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(T12:T17)</f>
+        <v>19.833333333333336</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(T12:T17)</f>
+        <v>0.47140452079103251</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>10.166666666666668</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(AD12:AD17)</f>
+        <v>9.8333333333333339</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(AD12:AD17)</f>
+        <v>0.47140452079103251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>78</v>
+      </c>
+      <c r="C13">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>82</v>
+      </c>
+      <c r="G13">
+        <v>96</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>16</v>
+      </c>
+      <c r="J13">
+        <v>84</v>
+      </c>
+      <c r="L13">
+        <v>87</v>
+      </c>
+      <c r="M13">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <v>44</v>
+      </c>
+      <c r="O13">
+        <v>56</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>19.5</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>9.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
   <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2419,7 +3234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AN99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5104,7 +5919,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5836,7 +6651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6429,7 +7244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AF36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7429,7 +8244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AF36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8430,7 +9245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8907,27 +9722,27 @@
       </c>
       <c r="AI12">
         <f>AVERAGE(Q16:Q24)</f>
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="AJ12">
         <f>_xlfn.STDEV.S(Q16:Q24)</f>
-        <v>1.5</v>
+        <v>2.8853076092506997</v>
       </c>
       <c r="AK12">
         <f>AVERAGE(R16:R24)</f>
-        <v>12.833333333333334</v>
+        <v>12</v>
       </c>
       <c r="AL12">
         <f>_xlfn.STDEV.S(R16:R24)</f>
-        <v>3.0138568866708555</v>
+        <v>2.4748737341529163</v>
       </c>
       <c r="AM12">
         <f>AVERAGE(S16:S24)</f>
-        <v>29.5</v>
+        <v>31.3</v>
       </c>
       <c r="AN12">
         <f>_xlfn.STDEV.S(S16:S24)</f>
-        <v>3.9686269665968861</v>
+        <v>3.8826537316634413</v>
       </c>
       <c r="AO12">
         <v>20.537037037037035</v>
@@ -9079,11 +9894,11 @@
         <v>3.9686269665968861</v>
       </c>
       <c r="AC16">
-        <f>AVERAGE(T16:T24)</f>
+        <f>AVERAGE(T16:T18)</f>
         <v>19.777777777777775</v>
       </c>
       <c r="AD16">
-        <f>_xlfn.STDEV.S(T16:T24)</f>
+        <f>_xlfn.STDEV.S(T16:T18)</f>
         <v>2.0838888148345602</v>
       </c>
       <c r="AE16">
@@ -9091,7 +9906,7 @@
         <v>6.9444444444444438</v>
       </c>
       <c r="AF16">
-        <f>_xlfn.STDEV.S(V16:V24)</f>
+        <f>_xlfn.STDEV.S(V16:V18)</f>
         <v>2.523959264800121</v>
       </c>
     </row>
@@ -9219,6 +10034,175 @@
         <v>9.8333333333333321</v>
       </c>
     </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>68</v>
+      </c>
+      <c r="C21">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>89</v>
+      </c>
+      <c r="G21">
+        <v>89</v>
+      </c>
+      <c r="H21">
+        <v>11</v>
+      </c>
+      <c r="I21">
+        <v>9</v>
+      </c>
+      <c r="J21">
+        <v>91</v>
+      </c>
+      <c r="L21">
+        <v>77</v>
+      </c>
+      <c r="M21">
+        <v>23</v>
+      </c>
+      <c r="N21">
+        <v>42</v>
+      </c>
+      <c r="O21">
+        <v>58</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" ref="Q19:Q22" si="6">AVERAGE(C21,D21)</f>
+        <v>21.5</v>
+      </c>
+      <c r="R21">
+        <f t="shared" ref="R19:R22" si="7">AVERAGE(H21:I21)</f>
+        <v>10</v>
+      </c>
+      <c r="S21">
+        <f t="shared" ref="S19:S22" si="8">AVERAGE(M21,N21)</f>
+        <v>32.5</v>
+      </c>
+      <c r="T21">
+        <f t="shared" ref="T19:T22" si="9">AVERAGE(Q21:S21)</f>
+        <v>21.333333333333332</v>
+      </c>
+      <c r="U21">
+        <f t="shared" ref="U19:U22" si="10">MIN(Q21:S21)</f>
+        <v>10</v>
+      </c>
+      <c r="V21">
+        <f t="shared" ref="V19:V22" si="11">(T21-U21)</f>
+        <v>11.333333333333332</v>
+      </c>
+      <c r="W21">
+        <f>AVERAGE(Q21:Q23)</f>
+        <v>17.75</v>
+      </c>
+      <c r="X21">
+        <f>_xlfn.STDEV.S(Q21:Q23)</f>
+        <v>5.3033008588991066</v>
+      </c>
+      <c r="Y21">
+        <f>AVERAGE(R21:R23)</f>
+        <v>10.75</v>
+      </c>
+      <c r="Z21">
+        <f>_xlfn.STDEV.S(R21:R23)</f>
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="AA21">
+        <f>AVERAGE(S21:S23)</f>
+        <v>34</v>
+      </c>
+      <c r="AB21">
+        <f>_xlfn.STDEV.S(S21:S23)</f>
+        <v>2.1213203435596424</v>
+      </c>
+      <c r="AC21">
+        <f>AVERAGE(T21:T23)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AD21">
+        <f>_xlfn.STDEV.S(T21:T23)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="AE21">
+        <f>AVERAGE(V21:V23)</f>
+        <v>10.083333333333332</v>
+      </c>
+      <c r="AF21">
+        <f>_xlfn.STDEV.S(V21:V23)</f>
+        <v>1.7677669529663689</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>81</v>
+      </c>
+      <c r="C22">
+        <v>19</v>
+      </c>
+      <c r="D22">
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <v>91</v>
+      </c>
+      <c r="G22">
+        <v>95</v>
+      </c>
+      <c r="H22">
+        <v>5</v>
+      </c>
+      <c r="I22">
+        <v>18</v>
+      </c>
+      <c r="J22">
+        <v>82</v>
+      </c>
+      <c r="L22">
+        <v>82</v>
+      </c>
+      <c r="M22">
+        <v>18</v>
+      </c>
+      <c r="N22">
+        <v>53</v>
+      </c>
+      <c r="O22">
+        <v>47</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="7"/>
+        <v>11.5</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="8"/>
+        <v>35.5</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="9"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="11"/>
+        <v>8.8333333333333321</v>
+      </c>
+    </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
@@ -10079,53 +11063,53 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q68" t="e">
-        <f t="shared" ref="Q68:Q109" si="6">AVERAGE(C68,D68)</f>
+        <f t="shared" ref="Q68:Q109" si="12">AVERAGE(C68,D68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R68" t="e">
-        <f t="shared" ref="R68:R109" si="7">AVERAGE(H68:I68)</f>
+        <f t="shared" ref="R68:R109" si="13">AVERAGE(H68:I68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S68" t="e">
-        <f t="shared" ref="S68:S109" si="8">AVERAGE(M68,N68)</f>
+        <f t="shared" ref="S68:S109" si="14">AVERAGE(M68,N68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T68" t="e">
-        <f t="shared" ref="T68:T109" si="9">AVERAGE(Q68:S68)</f>
+        <f t="shared" ref="T68:T109" si="15">AVERAGE(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U68" t="e">
-        <f t="shared" ref="U68:U109" si="10">MIN(Q68:S68)</f>
+        <f t="shared" ref="U68:U109" si="16">MIN(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" t="e">
-        <f t="shared" ref="V68:V109" si="11">(1/3)*(T68-U68)</f>
+        <f t="shared" ref="V68:V109" si="17">(1/3)*(T68-U68)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q69" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R69" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S69" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T69" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U69" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V69" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10141,27 +11125,27 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q73" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R73" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S73" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T73" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U73" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC73" t="e">
@@ -10183,53 +11167,53 @@
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q74" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R74" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S74" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T74" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V74" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q75" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R75" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S75" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T75" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U75" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V75" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10245,27 +11229,27 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q79" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R79" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S79" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T79" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U79" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC79" t="e">
@@ -10287,235 +11271,235 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q80" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R80" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S80" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T80" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U80" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V80" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q81" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R81" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S81" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T81" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U81" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V81" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q82" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R82" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S82" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T82" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U82" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V82" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q83" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R83" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S83" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T83" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U83" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V83" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q84" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R84" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S84" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T84" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U84" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V84" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q85" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R85" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S85" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T85" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U85" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q86" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R86" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S86" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T86" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U86" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V86" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q87" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R87" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S87" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T87" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U87" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V87" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q88" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R88" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S88" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T88" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V88" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10531,27 +11515,27 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q92" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R92" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S92" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T92" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U92" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V92" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC92" t="e">
@@ -10573,131 +11557,131 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q93" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R93" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S93" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T93" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U93" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V93" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q94" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R94" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S94" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T94" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U94" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V94" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q95" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S95" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T95" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U95" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V95" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q96" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R96" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S96" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T96" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U96" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V96" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q97" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R97" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S97" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T97" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V97" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10713,27 +11697,27 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q101" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R101" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S101" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T101" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U101" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V101" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC101" t="e">
@@ -10755,209 +11739,209 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q102" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R102" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S102" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T102" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U102" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q103" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R103" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S103" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T103" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U103" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q104" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R104" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S104" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T104" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U104" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V104" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q105" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R105" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S105" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T105" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U105" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q106" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R106" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S106" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T106" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q107" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R107" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S107" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T107" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U107" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q108" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R108" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S108" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T108" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U108" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q109" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S109" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T109" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U109" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10966,7 +11950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11268,6 +12252,230 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F457CA3F-CF30-4A83-B818-DAEC92077AB2}">
+  <dimension ref="B1:AF3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" t="s">
+        <v>45</v>
+      </c>
+      <c r="W1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>81</v>
+      </c>
+      <c r="C2">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>80</v>
+      </c>
+      <c r="G2">
+        <v>92</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
+      <c r="I2">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>83</v>
+      </c>
+      <c r="L2">
+        <v>82</v>
+      </c>
+      <c r="M2">
+        <v>18</v>
+      </c>
+      <c r="N2">
+        <v>48</v>
+      </c>
+      <c r="O2">
+        <v>52</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2" si="0">AVERAGE(C2,D2)</f>
+        <v>19.5</v>
+      </c>
+      <c r="R2">
+        <f t="shared" ref="R2" si="1">AVERAGE(H2,I2)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S2">
+        <f t="shared" ref="S2" si="2">AVERAGE(M2,N2)</f>
+        <v>33</v>
+      </c>
+      <c r="T2">
+        <f t="shared" ref="T2" si="3">AVERAGE(Q2:S2)</f>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="U2">
+        <f>AVERAGE(Q2:Q5)</f>
+        <v>19.5</v>
+      </c>
+      <c r="V2">
+        <f>_xlfn.STDEV.S(Q2:Q5)</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGE(R2:R5)</f>
+        <v>10.75</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.STDEV.S(R2:R5)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGE(S2:S5)</f>
+        <v>29</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.STDEV.S(S2:S5)</f>
+        <v>5.6568542494923806</v>
+      </c>
+      <c r="AA2">
+        <f>AVERAGE(T2:T5)</f>
+        <v>19.75</v>
+      </c>
+      <c r="AB2">
+        <f>_xlfn.STDEV.S(T2:T5)</f>
+        <v>2.7105759945484338</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" ref="AC2" si="4">MIN(Q2:S2)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD2">
+        <f t="shared" ref="AD2" si="5">(T2-AC2)</f>
+        <v>9.1666666666666679</v>
+      </c>
+      <c r="AE2">
+        <f>AVERAGE(AD2:AD5)</f>
+        <v>9</v>
+      </c>
+      <c r="AF2">
+        <f>_xlfn.STDEV.S(AD2:AD5)</f>
+        <v>0.2357022603955175</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>81</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>80</v>
+      </c>
+      <c r="G3">
+        <v>91</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>91</v>
+      </c>
+      <c r="L3">
+        <v>82</v>
+      </c>
+      <c r="M3">
+        <v>18</v>
+      </c>
+      <c r="N3">
+        <v>32</v>
+      </c>
+      <c r="O3">
+        <v>68</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3" si="6">AVERAGE(C3,D3)</f>
+        <v>19.5</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3" si="7">AVERAGE(H3,I3)</f>
+        <v>9</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3" si="8">AVERAGE(M3,N3)</f>
+        <v>25</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3" si="9">AVERAGE(Q3:S3)</f>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" ref="AC3" si="10">MIN(Q3:S3)</f>
+        <v>9</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" ref="AD3" si="11">(T3-AC3)</f>
+        <v>8.8333333333333321</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7986D54-7707-40F4-AFC2-8FFB01A635DF}">
   <dimension ref="B1:AF4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11553,7 +12761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
   <dimension ref="A2:AF17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12120,19 +13328,19 @@
         <v>57</v>
       </c>
       <c r="Q15">
-        <f t="shared" ref="Q11:Q17" si="17">AVERAGE(C15,D15)</f>
+        <f t="shared" ref="Q15:Q17" si="17">AVERAGE(C15,D15)</f>
         <v>19</v>
       </c>
       <c r="R15">
-        <f t="shared" ref="R11:R17" si="18">AVERAGE(H15,I15)</f>
+        <f t="shared" ref="R15:R17" si="18">AVERAGE(H15,I15)</f>
         <v>12.5</v>
       </c>
       <c r="S15">
-        <f t="shared" ref="S11:S17" si="19">AVERAGE(M15,N15)</f>
+        <f t="shared" ref="S15:S17" si="19">AVERAGE(M15,N15)</f>
         <v>29.5</v>
       </c>
       <c r="T15">
-        <f t="shared" ref="T11:T17" si="20">AVERAGE(Q15:S15)</f>
+        <f t="shared" ref="T15:T17" si="20">AVERAGE(Q15:S15)</f>
         <v>20.333333333333332</v>
       </c>
       <c r="U15">
@@ -12168,11 +13376,11 @@
         <v>1.8282758524338136</v>
       </c>
       <c r="AC15">
-        <f t="shared" ref="AC11:AC17" si="21">MIN(Q15:S15)</f>
+        <f t="shared" ref="AC15:AC17" si="21">MIN(Q15:S15)</f>
         <v>12.5</v>
       </c>
       <c r="AD15">
-        <f t="shared" ref="AD11:AD17" si="22">(T15-AC15)</f>
+        <f t="shared" ref="AD15:AD17" si="22">(T15-AC15)</f>
         <v>7.8333333333333321</v>
       </c>
       <c r="AE15">
@@ -12313,7 +13521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12479,7 +13687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
   <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12822,19 +14030,19 @@
         <v>56</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q7:Q13" si="6">AVERAGE(C12:D12)</f>
+        <f t="shared" ref="Q12:Q13" si="6">AVERAGE(C12:D12)</f>
         <v>19.5</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R7:R13" si="7">AVERAGE(H12:I12)</f>
+        <f t="shared" ref="R12:R13" si="7">AVERAGE(H12:I12)</f>
         <v>9</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S7:S13" si="8">AVERAGE(M12:N12)</f>
+        <f t="shared" ref="S12:S13" si="8">AVERAGE(M12:N12)</f>
         <v>26</v>
       </c>
       <c r="T12">
-        <f t="shared" ref="T7:T13" si="9">AVERAGE(Q12:S12)</f>
+        <f t="shared" ref="T12:T13" si="9">AVERAGE(Q12:S12)</f>
         <v>18.166666666666668</v>
       </c>
       <c r="U12">
@@ -12870,11 +14078,11 @@
         <v>1.2963624321753389</v>
       </c>
       <c r="AC12">
-        <f t="shared" ref="AC7:AC13" si="10">MIN(Q12:S12)</f>
+        <f t="shared" ref="AC12:AC13" si="10">MIN(Q12:S12)</f>
         <v>9</v>
       </c>
       <c r="AD12">
-        <f t="shared" ref="AD7:AD13" si="11">T12-AC12</f>
+        <f t="shared" ref="AD12:AD13" si="11">T12-AC12</f>
         <v>9.1666666666666679</v>
       </c>
       <c r="AE12">
@@ -12953,7 +14161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
   <dimension ref="A2:AF24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14085,7 +15293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14248,7 +15456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14673,493 +15881,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
-  <dimension ref="A2:AF9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>60</v>
-      </c>
-      <c r="C4">
-        <v>40</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>93</v>
-      </c>
-      <c r="G4">
-        <v>86</v>
-      </c>
-      <c r="H4">
-        <v>14</v>
-      </c>
-      <c r="I4">
-        <v>13</v>
-      </c>
-      <c r="J4">
-        <v>87</v>
-      </c>
-      <c r="L4">
-        <v>87</v>
-      </c>
-      <c r="M4">
-        <v>13</v>
-      </c>
-      <c r="N4">
-        <v>20</v>
-      </c>
-      <c r="O4">
-        <v>80</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>23.5</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>13.5</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>16.5</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>17.833333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q9)</f>
-        <v>19.583333333333332</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q9)</f>
-        <v>2.3540744819709287</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R9)</f>
-        <v>13.916666666666666</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R9)</f>
-        <v>2.5380438661825075</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S10)</f>
-        <v>23</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S9)</f>
-        <v>5.196152422706632</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T9)</f>
-        <v>18.833333333333332</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T9)</f>
-        <v>1.8737959096740264</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>13.5</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>4.3333333333333321</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD9)</f>
-        <v>4.916666666666667</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD9)</f>
-        <v>2.1337239225770932</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>73</v>
-      </c>
-      <c r="C5">
-        <v>27</v>
-      </c>
-      <c r="D5">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>85</v>
-      </c>
-      <c r="G5">
-        <v>84</v>
-      </c>
-      <c r="H5">
-        <v>16</v>
-      </c>
-      <c r="I5">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>82</v>
-      </c>
-      <c r="L5">
-        <v>78</v>
-      </c>
-      <c r="M5">
-        <v>22</v>
-      </c>
-      <c r="N5">
-        <v>23</v>
-      </c>
-      <c r="O5">
-        <v>77</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
-        <v>21</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
-        <v>17</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
-        <v>22.5</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
-        <v>20.166666666666668</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
-        <v>17</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD9" si="5">T5-AC5</f>
-        <v>3.1666666666666679</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>67</v>
-      </c>
-      <c r="C6">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>94</v>
-      </c>
-      <c r="G6">
-        <v>91</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>90</v>
-      </c>
-      <c r="L6">
-        <v>80</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-      <c r="N6">
-        <v>30</v>
-      </c>
-      <c r="O6">
-        <v>70</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>9.5</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>71</v>
-      </c>
-      <c r="C7">
-        <v>29</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>85</v>
-      </c>
-      <c r="H7">
-        <v>15</v>
-      </c>
-      <c r="I7">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>86</v>
-      </c>
-      <c r="L7">
-        <v>72</v>
-      </c>
-      <c r="M7">
-        <v>28</v>
-      </c>
-      <c r="N7">
-        <v>26</v>
-      </c>
-      <c r="O7">
-        <v>74</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>18.5</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>14.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>14.5</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>82</v>
-      </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>18</v>
-      </c>
-      <c r="E8">
-        <v>82</v>
-      </c>
-      <c r="G8">
-        <v>81</v>
-      </c>
-      <c r="H8">
-        <v>19</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>88</v>
-      </c>
-      <c r="L8">
-        <v>79</v>
-      </c>
-      <c r="M8">
-        <v>21</v>
-      </c>
-      <c r="N8">
-        <v>38</v>
-      </c>
-      <c r="O8">
-        <v>62</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>15.5</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>29.5</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>15.5</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>76</v>
-      </c>
-      <c r="C9">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>90</v>
-      </c>
-      <c r="G9">
-        <v>86</v>
-      </c>
-      <c r="H9">
-        <v>14</v>
-      </c>
-      <c r="I9">
-        <v>13</v>
-      </c>
-      <c r="J9">
-        <v>87</v>
-      </c>
-      <c r="L9">
-        <v>85</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-      <c r="N9">
-        <v>20</v>
-      </c>
-      <c r="O9">
-        <v>80</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>13.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>17.5</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>13.5</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>2.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>